--- a/Strategy_Roles_India_LinkedIn_Links.xlsx
+++ b/Strategy_Roles_India_LinkedIn_Links.xlsx
@@ -397,18 +397,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J234"/>
+  <dimension ref="A1:J484"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="55.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="80.83203125" customWidth="1"/>
+    <col min="1" max="1" width="34.83203125" customWidth="1"/>
+    <col min="2" max="2" width="68.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="90.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7899,9 +7899,8009 @@
         <v/>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>Salesforce</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Director, Strategy &amp; Enablement</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D235" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E235" t="str">
+        <v>Enterprise Software (SaaS)</v>
+      </c>
+      <c r="F235" t="str">
+        <v>$34.9B</v>
+      </c>
+      <c r="G235" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H235" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-strategy-enablement-at-salesforce-4466064067</v>
+      </c>
+      <c r="I235" t="str">
+        <v/>
+      </c>
+      <c r="J235" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Director - Corporate Strategy - New Delhi</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Delhi, India</v>
+      </c>
+      <c r="E236" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F236" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G236" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H236" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-sat-ami-sat-s-e-corporate-strategy-new-delhi-at-ey-4456577942</v>
+      </c>
+      <c r="I236" t="str">
+        <v/>
+      </c>
+      <c r="J236" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Director - Corporate Strategy - Bangalore</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D237" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E237" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F237" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G237" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H237" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-sat-tmt-sat-s-e-corporate-strategy-bangalore-at-ey-4467362693</v>
+      </c>
+      <c r="I237" t="str">
+        <v/>
+      </c>
+      <c r="J237" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Snapmint</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Director - Founder's Office</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Founder's Office</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E238" t="str">
+        <v>Social Media</v>
+      </c>
+      <c r="F238" t="str">
+        <v>$5B+</v>
+      </c>
+      <c r="G238" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H238" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-founder-s-office-at-snapmint-4476146445</v>
+      </c>
+      <c r="I238" t="str">
+        <v/>
+      </c>
+      <c r="J238" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Mastercard</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Vice President - Enterprise Value Strategy &amp; Transformation</v>
+      </c>
+      <c r="C239" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Pune Division, Maharashtra, India</v>
+      </c>
+      <c r="E239" t="str">
+        <v>Payments Technology</v>
+      </c>
+      <c r="F239" t="str">
+        <v>$25.1B</v>
+      </c>
+      <c r="G239" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H239" t="str">
+        <v>https://in.linkedin.com/jobs/view/vice-president-enterprise-value-strategy-transformation-at-mastercard-4471742874</v>
+      </c>
+      <c r="I239" t="str">
+        <v/>
+      </c>
+      <c r="J239" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Vice President - Strategy - Mumbai</v>
+      </c>
+      <c r="C240" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E240" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F240" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G240" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H240" t="str">
+        <v>https://in.linkedin.com/jobs/view/vice-president-sat-tmt-sat-s-e-strategy-mumbai-at-ey-4417208754</v>
+      </c>
+      <c r="I240" t="str">
+        <v/>
+      </c>
+      <c r="J240" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>HETERO LABS LIMITED</v>
+      </c>
+      <c r="B241" t="str">
+        <v>VP-Corporate Strategy &amp; Business Development</v>
+      </c>
+      <c r="C241" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D241" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E241" t="str">
+        <v>Pharmaceuticals</v>
+      </c>
+      <c r="F241" t="str">
+        <v>$1.5B+</v>
+      </c>
+      <c r="G241" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H241" t="str">
+        <v>https://in.linkedin.com/jobs/view/hiring-for-vp-corporate-strategy-business-development-%E2%80%93-emerging-markets-at-hetero-labs-limited-india-4470904750</v>
+      </c>
+      <c r="I241" t="str">
+        <v/>
+      </c>
+      <c r="J241" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>Firework</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Chief of Staff (Office of the CBO)</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Chief of Staff</v>
+      </c>
+      <c r="D242" t="str">
+        <v>India</v>
+      </c>
+      <c r="E242" t="str">
+        <v>Video Commerce (SaaS)</v>
+      </c>
+      <c r="F242" t="str">
+        <v>$100M+</v>
+      </c>
+      <c r="G242" t="str">
+        <v>3-7 years</v>
+      </c>
+      <c r="H242" t="str">
+        <v>https://in.linkedin.com/jobs/view/chief-of-staff-office-of-the-cbo-at-firework-4466417194</v>
+      </c>
+      <c r="I242" t="str">
+        <v/>
+      </c>
+      <c r="J242" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Graviton Research Capital</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Chief of Staff, Partners' Office</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Chief of Staff</v>
+      </c>
+      <c r="D243" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E243" t="str">
+        <v>Quantitative Trading</v>
+      </c>
+      <c r="F243" t="str">
+        <v>$500M+</v>
+      </c>
+      <c r="G243" t="str">
+        <v>3-7 years</v>
+      </c>
+      <c r="H243" t="str">
+        <v>https://in.linkedin.com/jobs/view/chief-of-staff-partners-office-at-graviton-research-capital-4471473154</v>
+      </c>
+      <c r="I243" t="str">
+        <v/>
+      </c>
+      <c r="J243" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>Licious</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Director - Founder's office</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Founder's Office</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E244" t="str">
+        <v>D2C (Food)</v>
+      </c>
+      <c r="F244" t="str">
+        <v>$200M+</v>
+      </c>
+      <c r="G244" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H244" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-founder-s-office-at-licious-4471039480</v>
+      </c>
+      <c r="I244" t="str">
+        <v/>
+      </c>
+      <c r="J244" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>ANSR</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Director - Consulting &amp; Insights</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E245" t="str">
+        <v>GCC Advisory</v>
+      </c>
+      <c r="F245" t="str">
+        <v>$200M+</v>
+      </c>
+      <c r="G245" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H245" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-consulting-insights-at-ansr-4469750679</v>
+      </c>
+      <c r="I245" t="str">
+        <v/>
+      </c>
+      <c r="J245" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>Epsilon</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Vice President- HR Strategy, Analytics &amp; Insights</v>
+      </c>
+      <c r="C246" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E246" t="str">
+        <v>Data-Driven Marketing</v>
+      </c>
+      <c r="F246" t="str">
+        <v>$4B+</v>
+      </c>
+      <c r="G246" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H246" t="str">
+        <v>https://in.linkedin.com/jobs/view/vice-president-hr-strategy-analytics-insights-at-epsilon-4474600143</v>
+      </c>
+      <c r="I246" t="str">
+        <v/>
+      </c>
+      <c r="J246" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>GMR Group</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Head - Strategic Planning Group</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Goa, Goa, India</v>
+      </c>
+      <c r="E247" t="str">
+        <v>Infrastructure &amp; Airports</v>
+      </c>
+      <c r="F247" t="str">
+        <v>$2B+</v>
+      </c>
+      <c r="G247" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H247" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-strategic-planning-group-at-gmr-group-4472497608</v>
+      </c>
+      <c r="I247" t="str">
+        <v/>
+      </c>
+      <c r="J247" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>JPMorganChase</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Strategy - Executive Director</v>
+      </c>
+      <c r="C248" t="str">
+        <v>MD/ED</v>
+      </c>
+      <c r="D248" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E248" t="str">
+        <v>Banking &amp; Financial Services</v>
+      </c>
+      <c r="F248" t="str">
+        <v>$177.6B</v>
+      </c>
+      <c r="G248" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H248" t="str">
+        <v>https://in.linkedin.com/jobs/view/commercial-investment-bank-strategy-executive-director-at-jpmorganchase-4460577328</v>
+      </c>
+      <c r="I248" t="str">
+        <v/>
+      </c>
+      <c r="J248" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>HETERO LABS LIMITED</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Senior Vice President - BD, Joint Ventures &amp; M&amp;A</v>
+      </c>
+      <c r="C249" t="str">
+        <v>SVP</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E249" t="str">
+        <v>Pharmaceuticals</v>
+      </c>
+      <c r="F249" t="str">
+        <v>$1.5B+</v>
+      </c>
+      <c r="G249" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H249" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-vice-president-bd-joint-ventures-m-a-at-hetero-labs-4470901922</v>
+      </c>
+      <c r="I249" t="str">
+        <v/>
+      </c>
+      <c r="J249" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Vice President - Corporate Strategy - New Delhi</v>
+      </c>
+      <c r="C250" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D250" t="str">
+        <v>Delhi, India</v>
+      </c>
+      <c r="E250" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F250" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G250" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H250" t="str">
+        <v>https://in.linkedin.com/jobs/view/vice-president-corporate-strategy-new-delhi-at-ey-4466228380</v>
+      </c>
+      <c r="I250" t="str">
+        <v/>
+      </c>
+      <c r="J250" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Zamp</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Founder's Office, Strategy &amp; Operations</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Founder's Office</v>
+      </c>
+      <c r="D251" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E251" t="str">
+        <v>QSR (Burger King India)</v>
+      </c>
+      <c r="F251" t="str">
+        <v>$100M+</v>
+      </c>
+      <c r="G251" t="str">
+        <v>1-5 years</v>
+      </c>
+      <c r="H251" t="str">
+        <v>https://in.linkedin.com/jobs/view/founder-s-office-strategy-operations-at-zamp-4467879051</v>
+      </c>
+      <c r="I251" t="str">
+        <v/>
+      </c>
+      <c r="J251" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Epsilon</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Senior Advisor Strategy and Operations</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D252" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E252" t="str">
+        <v>Data-Driven Marketing</v>
+      </c>
+      <c r="F252" t="str">
+        <v>$4B+</v>
+      </c>
+      <c r="G252" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H252" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-advisor-strategy-and-operations-at-epsilon-4440690206</v>
+      </c>
+      <c r="I252" t="str">
+        <v/>
+      </c>
+      <c r="J252" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Alvarez &amp; Marsal</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Director - Merger Integration and Carve Out</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D253" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E253" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F253" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G253" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H253" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-merger-integration-carve-out-at-alvarez-marsal-4440996383</v>
+      </c>
+      <c r="I253" t="str">
+        <v/>
+      </c>
+      <c r="J253" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Alvarez &amp; Marsal</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Director - Merger Integration and Carve Out</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D254" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E254" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F254" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G254" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H254" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-merger-integration-carve-out-at-alvarez-marsal-mumbai-4440985740</v>
+      </c>
+      <c r="I254" t="str">
+        <v/>
+      </c>
+      <c r="J254" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Alvarez &amp; Marsal</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Director - Merger Integration and Carve Out</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D255" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E255" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F255" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G255" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H255" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-merger-integration-carve-out-at-alvarez-marsal-blr-4441203165</v>
+      </c>
+      <c r="I255" t="str">
+        <v/>
+      </c>
+      <c r="J255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>M3M India Private Limited</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Head - Transactions Advisory &amp; Acquisitions</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D256" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E256" t="str">
+        <v>Real Estate</v>
+      </c>
+      <c r="F256" t="str">
+        <v>$1B+</v>
+      </c>
+      <c r="G256" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H256" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-transactions-advisory-acquisitions-at-m3m-4475755638</v>
+      </c>
+      <c r="I256" t="str">
+        <v/>
+      </c>
+      <c r="J256" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Walmart</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Sr Manager, Business strategy &amp; PMO</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Sr Manager</v>
+      </c>
+      <c r="D257" t="str">
+        <v>Greater Bengaluru Area</v>
+      </c>
+      <c r="E257" t="str">
+        <v>Retail</v>
+      </c>
+      <c r="F257" t="str">
+        <v>$611B+</v>
+      </c>
+      <c r="G257" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H257" t="str">
+        <v>https://in.linkedin.com/jobs/view/sr-manager-business-strategy-pmo-at-walmart-4467843912</v>
+      </c>
+      <c r="I257" t="str">
+        <v/>
+      </c>
+      <c r="J257" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B258" t="str">
+        <v>CEO Advisory - Manager</v>
+      </c>
+      <c r="C258" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D258" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E258" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F258" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G258" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H258" t="str">
+        <v>https://in.linkedin.com/jobs/view/ceo-advisory-manager-at-accenture-4455359686</v>
+      </c>
+      <c r="I258" t="str">
+        <v/>
+      </c>
+      <c r="J258" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Strategy-Transaction Advisory - Manager</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D259" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E259" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F259" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G259" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H259" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-transaction-advisory-manager-at-accenture-4448328352</v>
+      </c>
+      <c r="I259" t="str">
+        <v/>
+      </c>
+      <c r="J259" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>PwC Acceleration Center India</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Manager - Strategy</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D260" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E260" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F260" t="str">
+        <v>$55.4B</v>
+      </c>
+      <c r="G260" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H260" t="str">
+        <v>https://in.linkedin.com/jobs/view/manager-strategy-at-pwc-acceleration-center-india-4466676461</v>
+      </c>
+      <c r="I260" t="str">
+        <v/>
+      </c>
+      <c r="J260" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>PwC Acceleration Center India</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Manager_Deals Strategy</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D261" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E261" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F261" t="str">
+        <v>$55.4B</v>
+      </c>
+      <c r="G261" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H261" t="str">
+        <v>https://in.linkedin.com/jobs/view/manager-deals-strategy-at-pwc-acceleration-center-india-4427851309</v>
+      </c>
+      <c r="I261" t="str">
+        <v/>
+      </c>
+      <c r="J261" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Alvarez &amp; Marsal</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Director - AIG</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D262" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E262" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F262" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G262" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H262" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-aig-at-alvarez-marsal-4440985750</v>
+      </c>
+      <c r="I262" t="str">
+        <v/>
+      </c>
+      <c r="J262" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Alvarez &amp; Marsal</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Manager, Technology Transformation Advisory</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D263" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E263" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F263" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G263" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H263" t="str">
+        <v>https://in.linkedin.com/jobs/view/manager-technology-transformation-advisory-at-alvarez-marsal-4474585791</v>
+      </c>
+      <c r="I263" t="str">
+        <v/>
+      </c>
+      <c r="J263" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>BCG</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Global Sector Senior Manager - Payments &amp; Fintech</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Sr Manager</v>
+      </c>
+      <c r="D264" t="str">
+        <v>Gurgaon, Haryana, India</v>
+      </c>
+      <c r="E264" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F264" t="str">
+        <v>$12B+</v>
+      </c>
+      <c r="G264" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H264" t="str">
+        <v>https://in.linkedin.com/jobs/view/global-sector-senior-manager-payments-fintech-at-bcg-4464848325</v>
+      </c>
+      <c r="I264" t="str">
+        <v/>
+      </c>
+      <c r="J264" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Portage Point Partners</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Director, Investment Banking</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D265" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E265" t="str">
+        <v>Restructuring Advisory</v>
+      </c>
+      <c r="F265" t="str">
+        <v>$200M+</v>
+      </c>
+      <c r="G265" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H265" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-investment-banking-at-portage-point-partners-4426000119</v>
+      </c>
+      <c r="I265" t="str">
+        <v/>
+      </c>
+      <c r="J265" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Cushman &amp; Wakefield</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Director / Senior Director - Healthcare Investment Transactions</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Sr Director</v>
+      </c>
+      <c r="D266" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E266" t="str">
+        <v>Real Estate Services</v>
+      </c>
+      <c r="F266" t="str">
+        <v>$9.5B</v>
+      </c>
+      <c r="G266" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H266" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-healthcare-investment-transactions-at-cushman-wakefield-4474302010</v>
+      </c>
+      <c r="I266" t="str">
+        <v/>
+      </c>
+      <c r="J266" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Corporate Strategy Manager Copy 01</v>
+      </c>
+      <c r="C267" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D267" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E267" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F267" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G267" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H267" t="str">
+        <v>https://in.linkedin.com/jobs/view/corporate-strategy-manager-copy-01-at-accenture-in-india-4461266842</v>
+      </c>
+      <c r="I267" t="str">
+        <v/>
+      </c>
+      <c r="J267" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>HSBC</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Vice President, Equities Chief Operating Officer</v>
+      </c>
+      <c r="C268" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D268" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E268" t="str">
+        <v>Banking</v>
+      </c>
+      <c r="F268" t="str">
+        <v>$66B+</v>
+      </c>
+      <c r="G268" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H268" t="str">
+        <v>https://in.linkedin.com/jobs/view/vice-president-equities-chief-operating-officer-at-hsbc-4465679034</v>
+      </c>
+      <c r="I268" t="str">
+        <v/>
+      </c>
+      <c r="J268" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Morgan Stanley</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Global Stewardship Team, Vice President, Investment Management</v>
+      </c>
+      <c r="C269" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D269" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E269" t="str">
+        <v>Investment Banking</v>
+      </c>
+      <c r="F269" t="str">
+        <v>$54.1B</v>
+      </c>
+      <c r="G269" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H269" t="str">
+        <v>https://in.linkedin.com/jobs/view/global-stewardship-team-vice-president-investment-management-at-morgan-stanley-4459145032</v>
+      </c>
+      <c r="I269" t="str">
+        <v/>
+      </c>
+      <c r="J269" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>Adani Realty</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Vice President - Operations</v>
+      </c>
+      <c r="C270" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D270" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E270" t="str">
+        <v>Real Estate (Adani)</v>
+      </c>
+      <c r="F270" t="str">
+        <v>$30B+</v>
+      </c>
+      <c r="G270" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H270" t="str">
+        <v>https://in.linkedin.com/jobs/view/vice-president-%E2%80%93-operations-at-adani-realty-4407909472</v>
+      </c>
+      <c r="I270" t="str">
+        <v/>
+      </c>
+      <c r="J270" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Visa</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Director, Business Development</v>
+      </c>
+      <c r="C271" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D271" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E271" t="str">
+        <v>Payments Technology</v>
+      </c>
+      <c r="F271" t="str">
+        <v>$32.7B</v>
+      </c>
+      <c r="G271" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H271" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-business-development-at-visa-4450326001</v>
+      </c>
+      <c r="I271" t="str">
+        <v/>
+      </c>
+      <c r="J271" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>GMR Group</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Executive Assistant - Corporate Chairman (Sports)</v>
+      </c>
+      <c r="C272" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D272" t="str">
+        <v>Delhi, Delhi, India</v>
+      </c>
+      <c r="E272" t="str">
+        <v>Infrastructure &amp; Airports</v>
+      </c>
+      <c r="F272" t="str">
+        <v>$2B+</v>
+      </c>
+      <c r="G272" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H272" t="str">
+        <v>https://in.linkedin.com/jobs/view/executive-assistant-corporate-chairman-sports-at-gmr-group-4476315494</v>
+      </c>
+      <c r="I272" t="str">
+        <v/>
+      </c>
+      <c r="J272" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Finkraft</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Associate Chief of Staff</v>
+      </c>
+      <c r="C273" t="str">
+        <v>Chief of Staff</v>
+      </c>
+      <c r="D273" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E273" t="str">
+        <v>Fintech (GST)</v>
+      </c>
+      <c r="F273" t="str">
+        <v>$100M+</v>
+      </c>
+      <c r="G273" t="str">
+        <v>3-7 years</v>
+      </c>
+      <c r="H273" t="str">
+        <v>https://in.linkedin.com/jobs/view/associate-chief-of-staff-at-finkraft-4443183067</v>
+      </c>
+      <c r="I273" t="str">
+        <v/>
+      </c>
+      <c r="J273" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>LogiNext</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Vice President - Business Development</v>
+      </c>
+      <c r="C274" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D274" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E274" t="str">
+        <v>Logistics SaaS</v>
+      </c>
+      <c r="F274" t="str">
+        <v>$100M+</v>
+      </c>
+      <c r="G274" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H274" t="str">
+        <v>https://in.linkedin.com/jobs/view/vice-president-business-development-at-loginext-4453096640</v>
+      </c>
+      <c r="I274" t="str">
+        <v/>
+      </c>
+      <c r="J274" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>PwC India</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Director_Enterprise Transformation Architect_Advisory</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D275" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E275" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F275" t="str">
+        <v>$55.4B</v>
+      </c>
+      <c r="G275" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H275" t="str">
+        <v>https://in.linkedin.com/jobs/view/in-director-enterprise-transformation-architect-da-central-advisory-bangalore-at-pwc-india-4476155259</v>
+      </c>
+      <c r="I275" t="str">
+        <v/>
+      </c>
+      <c r="J275" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>UST</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Director I - Consulting</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D276" t="str">
+        <v>Trivandrum, Kerala, India</v>
+      </c>
+      <c r="E276" t="str">
+        <v>Conglomerate</v>
+      </c>
+      <c r="F276" t="str">
+        <v>$100B+</v>
+      </c>
+      <c r="G276" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H276" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-i-consulting-tvm-hyd-at-ust-4449549344</v>
+      </c>
+      <c r="I276" t="str">
+        <v/>
+      </c>
+      <c r="J276" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>ANSR</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Consulting &amp; Insights - Director</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D277" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E277" t="str">
+        <v>GCC Advisory</v>
+      </c>
+      <c r="F277" t="str">
+        <v>$200M+</v>
+      </c>
+      <c r="G277" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H277" t="str">
+        <v>https://in.linkedin.com/jobs/view/consulting-insights-director-t500-29562-at-ansr-4470413779</v>
+      </c>
+      <c r="I277" t="str">
+        <v/>
+      </c>
+      <c r="J277" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Tata Consumer Products</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Director - Digital Transformation, Integrated Finance</v>
+      </c>
+      <c r="C278" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D278" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E278" t="str">
+        <v>FMCG</v>
+      </c>
+      <c r="F278" t="str">
+        <v>$2B+</v>
+      </c>
+      <c r="G278" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H278" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-%E2%80%93-digital-transformation-integrated-finance-at-tata-consumer-products-4469850542</v>
+      </c>
+      <c r="I278" t="str">
+        <v/>
+      </c>
+      <c r="J278" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Director - Business Consulting - Transformation Delivery</v>
+      </c>
+      <c r="C279" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D279" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E279" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F279" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G279" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H279" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-business-consulting-pi-fs-cns-bc-transformation-delivery-mumbai-at-ey-4468973979</v>
+      </c>
+      <c r="I279" t="str">
+        <v/>
+      </c>
+      <c r="J279" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Director - Business Consulting - Finance</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D280" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E280" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F280" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G280" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H280" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-business-consulting-pi-tmt-cns-bc-finance-bangalore-at-ey-4472965387</v>
+      </c>
+      <c r="I280" t="str">
+        <v/>
+      </c>
+      <c r="J280" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>PwC India</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Executive Director_Finance Transformation_Advisory</v>
+      </c>
+      <c r="C281" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D281" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E281" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F281" t="str">
+        <v>$55.4B</v>
+      </c>
+      <c r="G281" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H281" t="str">
+        <v>https://in.linkedin.com/jobs/view/in-executive-director-finance-transformation-finance-transformation-advisory-mumbai-at-pwc-india-4475954397</v>
+      </c>
+      <c r="I281" t="str">
+        <v/>
+      </c>
+      <c r="J281" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B282" t="str">
+        <v>GDS Executive Director - Finance, Digital &amp; Business Transformation</v>
+      </c>
+      <c r="C282" t="str">
+        <v>MD/ED</v>
+      </c>
+      <c r="D282" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E282" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F282" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G282" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H282" t="str">
+        <v>https://in.linkedin.com/jobs/view/gds-executive-director-finance-digital-business-transformation-at-ey-4474448300</v>
+      </c>
+      <c r="I282" t="str">
+        <v/>
+      </c>
+      <c r="J282" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>WSP in India</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Head -Advisory, UK GCC</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D283" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E283" t="str">
+        <v>Engineering Consulting</v>
+      </c>
+      <c r="F283" t="str">
+        <v>$12B+</v>
+      </c>
+      <c r="G283" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H283" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-advisory-uk-gcc-at-wsp-in-india-4451180732</v>
+      </c>
+      <c r="I283" t="str">
+        <v/>
+      </c>
+      <c r="J283" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>WSP in India</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Head -Advisory, UK GCC</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D284" t="str">
+        <v>Noida, Uttar Pradesh, India</v>
+      </c>
+      <c r="E284" t="str">
+        <v>Engineering Consulting</v>
+      </c>
+      <c r="F284" t="str">
+        <v>$12B+</v>
+      </c>
+      <c r="G284" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H284" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-advisory-uk-gcc-at-wsp-in-india-4464543058</v>
+      </c>
+      <c r="I284" t="str">
+        <v/>
+      </c>
+      <c r="J284" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>VOIS</v>
+      </c>
+      <c r="B285" t="str">
+        <v>GM -Lead Business Consultant</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D285" t="str">
+        <v>Pune Division, Maharashtra, India</v>
+      </c>
+      <c r="E285" t="str">
+        <v>Telecom (Vodafone Group)</v>
+      </c>
+      <c r="F285" t="str">
+        <v>$18B+</v>
+      </c>
+      <c r="G285" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H285" t="str">
+        <v>https://in.linkedin.com/jobs/view/gm-lead-business-consultant-at-vois-4466224206</v>
+      </c>
+      <c r="I285" t="str">
+        <v/>
+      </c>
+      <c r="J285" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Mastercard</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Senior Specialist, Strategy Pricing &amp; Interchange</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D286" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E286" t="str">
+        <v>Payments Technology</v>
+      </c>
+      <c r="F286" t="str">
+        <v>$25.1B</v>
+      </c>
+      <c r="G286" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H286" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-specialist-strategy-pricing-interchange-at-mastercard-4477157110</v>
+      </c>
+      <c r="I286" t="str">
+        <v/>
+      </c>
+      <c r="J286" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B287" t="str">
+        <v>GN-I&amp;E CEO Advisory - Consultant</v>
+      </c>
+      <c r="C287" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D287" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E287" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F287" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G287" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H287" t="str">
+        <v>https://in.linkedin.com/jobs/view/gn-i-e-ceo-advisory-consultant-at-accenture-in-india-4455361646</v>
+      </c>
+      <c r="I287" t="str">
+        <v/>
+      </c>
+      <c r="J287" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Salesforce</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Manager/Senior Manager - Business Strategy</v>
+      </c>
+      <c r="C288" t="str">
+        <v>Sr Manager</v>
+      </c>
+      <c r="D288" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E288" t="str">
+        <v>Enterprise Software (SaaS)</v>
+      </c>
+      <c r="F288" t="str">
+        <v>$34.9B</v>
+      </c>
+      <c r="G288" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H288" t="str">
+        <v>https://in.linkedin.com/jobs/view/manager-senior-manager-business-strategy-at-salesforce-4472460025</v>
+      </c>
+      <c r="I288" t="str">
+        <v/>
+      </c>
+      <c r="J288" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Business Transformation Manager</v>
+      </c>
+      <c r="C289" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D289" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E289" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F289" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G289" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H289" t="str">
+        <v>https://in.linkedin.com/jobs/view/business-transformation-manager-at-accenture-in-india-4448350329</v>
+      </c>
+      <c r="I289" t="str">
+        <v/>
+      </c>
+      <c r="J289" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Oliver Wyman</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Oliver Wyman - Engagement Manager - Mumbai/Gurugram</v>
+      </c>
+      <c r="C290" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D290" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E290" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F290" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G290" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H290" t="str">
+        <v>https://in.linkedin.com/jobs/view/oliver-wyman-engagement-manager-mumbai-gurugram-at-oliver-wyman-4460365105</v>
+      </c>
+      <c r="I290" t="str">
+        <v/>
+      </c>
+      <c r="J290" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Enterprise AI Value Strategy - Manager</v>
+      </c>
+      <c r="C291" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D291" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E291" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F291" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G291" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H291" t="str">
+        <v>https://in.linkedin.com/jobs/view/s-c-gn-ts-t-%E2%80%93enterprise-ai-value-strategy-manager-at-accenture-in-india-4450768533</v>
+      </c>
+      <c r="I291" t="str">
+        <v/>
+      </c>
+      <c r="J291" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Enterprise AI Value Strategy - Manager</v>
+      </c>
+      <c r="C292" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D292" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E292" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F292" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G292" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H292" t="str">
+        <v>https://in.linkedin.com/jobs/view/s-c-gn-ts-t-%E2%80%93enterprise-ai-value-strategy-manager-at-accenture-in-india-4450759734</v>
+      </c>
+      <c r="I292" t="str">
+        <v/>
+      </c>
+      <c r="J292" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Finkraft</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Founder's Office-Associate</v>
+      </c>
+      <c r="C293" t="str">
+        <v>Founder's Office</v>
+      </c>
+      <c r="D293" t="str">
+        <v>Bangalore Urban, Karnataka, India</v>
+      </c>
+      <c r="E293" t="str">
+        <v>Fintech (GST)</v>
+      </c>
+      <c r="F293" t="str">
+        <v>$100M+</v>
+      </c>
+      <c r="G293" t="str">
+        <v>1-5 years</v>
+      </c>
+      <c r="H293" t="str">
+        <v>https://in.linkedin.com/jobs/view/founder-s-office-associate-at-finkraft-4433460474</v>
+      </c>
+      <c r="I293" t="str">
+        <v/>
+      </c>
+      <c r="J293" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Alvarez &amp; Marsal</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Director - CDD</v>
+      </c>
+      <c r="C294" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D294" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E294" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F294" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G294" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H294" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-cdd-at-alvarez-marsal-4449662777</v>
+      </c>
+      <c r="I294" t="str">
+        <v/>
+      </c>
+      <c r="J294" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Cognizant</v>
+      </c>
+      <c r="B295" t="str">
+        <v>SBU Head - Practice</v>
+      </c>
+      <c r="C295" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D295" t="str">
+        <v>Bangalore Urban, Karnataka, India</v>
+      </c>
+      <c r="E295" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F295" t="str">
+        <v>$19.4B</v>
+      </c>
+      <c r="G295" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H295" t="str">
+        <v>https://in.linkedin.com/jobs/view/sbu-head-practice-at-cognizant-4444021397</v>
+      </c>
+      <c r="I295" t="str">
+        <v/>
+      </c>
+      <c r="J295" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>upGrad Rekrut</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Strategic Executive Assistant - C Suite</v>
+      </c>
+      <c r="C296" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D296" t="str">
+        <v>New Delhi, Delhi, India</v>
+      </c>
+      <c r="E296" t="str">
+        <v>EdTech</v>
+      </c>
+      <c r="F296" t="str">
+        <v>$200M+</v>
+      </c>
+      <c r="G296" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H296" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategic-executive-assistant-c-suite-at-upgrad-rekrut-4473603783</v>
+      </c>
+      <c r="I296" t="str">
+        <v/>
+      </c>
+      <c r="J296" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Specialist Executive Manager, Financial Planning and Analysis</v>
+      </c>
+      <c r="C297" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D297" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E297" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F297" t="str">
+        <v>$67.2B</v>
+      </c>
+      <c r="G297" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H297" t="str">
+        <v>https://in.linkedin.com/jobs/view/specialist-executive-manager-financial-planning-and-analysis-at-deloitte-4457951810</v>
+      </c>
+      <c r="I297" t="str">
+        <v/>
+      </c>
+      <c r="J297" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Amgen</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Global Markets &amp; Policy Finance Director</v>
+      </c>
+      <c r="C298" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D298" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E298" t="str">
+        <v>Biotechnology</v>
+      </c>
+      <c r="F298" t="str">
+        <v>$27B+</v>
+      </c>
+      <c r="G298" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H298" t="str">
+        <v>https://in.linkedin.com/jobs/view/global-markets-policy-finance-director-at-amgen-4471864979</v>
+      </c>
+      <c r="I298" t="str">
+        <v/>
+      </c>
+      <c r="J298" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>Revolut</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Strategy &amp; Operations Manager (Crypto)</v>
+      </c>
+      <c r="C299" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D299" t="str">
+        <v>Indore, Madhya Pradesh, India</v>
+      </c>
+      <c r="E299" t="str">
+        <v>Fintech</v>
+      </c>
+      <c r="F299" t="str">
+        <v>$2.2B+</v>
+      </c>
+      <c r="G299" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H299" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-operations-manager-crypto-at-revolut-4445770207</v>
+      </c>
+      <c r="I299" t="str">
+        <v/>
+      </c>
+      <c r="J299" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Zamp</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Founder's Office, Zamp - Strategy &amp; Operations</v>
+      </c>
+      <c r="C300" t="str">
+        <v>Founder's Office</v>
+      </c>
+      <c r="D300" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E300" t="str">
+        <v>QSR (Burger King India)</v>
+      </c>
+      <c r="F300" t="str">
+        <v>$100M+</v>
+      </c>
+      <c r="G300" t="str">
+        <v>1-5 years</v>
+      </c>
+      <c r="H300" t="str">
+        <v>https://in.linkedin.com/jobs/view/founder-s-office-zamp-strategy-operations-at-zamp-4475982008</v>
+      </c>
+      <c r="I300" t="str">
+        <v/>
+      </c>
+      <c r="J300" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B301" t="str">
+        <v>#ACN I&amp;P GN I&amp;EHealth Health Admin Consultant</v>
+      </c>
+      <c r="C301" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D301" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E301" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F301" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G301" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H301" t="str">
+        <v>https://in.linkedin.com/jobs/view/acn-i-p-gn-i-ehealth-health-admin-consultant-at-accenture-in-india-4448320514</v>
+      </c>
+      <c r="I301" t="str">
+        <v/>
+      </c>
+      <c r="J301" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B302" t="str">
+        <v>GN-Capital Markets-Consultant</v>
+      </c>
+      <c r="C302" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D302" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E302" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F302" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G302" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H302" t="str">
+        <v>https://in.linkedin.com/jobs/view/gn-capital-markets-consultant-at-accenture-in-india-4448344092</v>
+      </c>
+      <c r="I302" t="str">
+        <v/>
+      </c>
+      <c r="J302" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>McKinsey &amp; Company</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Knowledge Analyst - Healthcare Access, Quality, and Outcomes</v>
+      </c>
+      <c r="C303" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="D303" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E303" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F303" t="str">
+        <v>$16B+</v>
+      </c>
+      <c r="G303" t="str">
+        <v>0-2 years</v>
+      </c>
+      <c r="H303" t="str">
+        <v>https://in.linkedin.com/jobs/view/knowledge-analyst-healthcare-access-quality-and-outcomes-at-mckinsey-company-4472762717</v>
+      </c>
+      <c r="I303" t="str">
+        <v/>
+      </c>
+      <c r="J303" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B304" t="str">
+        <v>GN - Management Consulting - CFO&amp;EV - Analyst</v>
+      </c>
+      <c r="C304" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D304" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E304" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F304" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G304" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H304" t="str">
+        <v>https://in.linkedin.com/jobs/view/gn-mangement-consulting-cfo-ev-analyst-at-accenture-in-india-4448323526</v>
+      </c>
+      <c r="I304" t="str">
+        <v/>
+      </c>
+      <c r="J304" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B305" t="str">
+        <v>GN - Management Consulting - CFO&amp;EV - Analyst</v>
+      </c>
+      <c r="C305" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D305" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E305" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F305" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G305" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H305" t="str">
+        <v>https://in.linkedin.com/jobs/view/gn-mangement-consulting-cfo-ev-analyst-at-accenture-in-india-4448336438</v>
+      </c>
+      <c r="I305" t="str">
+        <v/>
+      </c>
+      <c r="J305" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B306" t="str">
+        <v>GN - Management Consulting - CFO&amp;EV - Analyst</v>
+      </c>
+      <c r="C306" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D306" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E306" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F306" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G306" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H306" t="str">
+        <v>https://in.linkedin.com/jobs/view/gn-mangement-consulting-cfo-ev-analyst-at-accenture-in-india-4448340184</v>
+      </c>
+      <c r="I306" t="str">
+        <v/>
+      </c>
+      <c r="J306" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B307" t="str">
+        <v>GN - Management Consulting - CFO&amp;EV - Analyst</v>
+      </c>
+      <c r="C307" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D307" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E307" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F307" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G307" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H307" t="str">
+        <v>https://in.linkedin.com/jobs/view/gn-mangement-consulting-cfo-ev-analyst-at-accenture-in-india-4448333494</v>
+      </c>
+      <c r="I307" t="str">
+        <v/>
+      </c>
+      <c r="J307" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B308" t="str">
+        <v>GN - Management Consulting - CFO&amp;EV - Analyst</v>
+      </c>
+      <c r="C308" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D308" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E308" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F308" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G308" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H308" t="str">
+        <v>https://in.linkedin.com/jobs/view/gn-mangement-consulting-cfo-ev-analyst-at-accenture-in-india-4448317917</v>
+      </c>
+      <c r="I308" t="str">
+        <v/>
+      </c>
+      <c r="J308" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Ujjivan Small Finance Bank</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Manager - Transformation</v>
+      </c>
+      <c r="C309" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D309" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E309" t="str">
+        <v>Banking (SFB)</v>
+      </c>
+      <c r="F309" t="str">
+        <v>$800M+</v>
+      </c>
+      <c r="G309" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H309" t="str">
+        <v>https://in.linkedin.com/jobs/view/manager-transformation-at-ujjivan-small-finance-bank-4464507804</v>
+      </c>
+      <c r="I309" t="str">
+        <v/>
+      </c>
+      <c r="J309" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Business Transformation Manager</v>
+      </c>
+      <c r="C310" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D310" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E310" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F310" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G310" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H310" t="str">
+        <v>https://in.linkedin.com/jobs/view/business-transformation-manager-at-accenture-in-india-4462409427</v>
+      </c>
+      <c r="I310" t="str">
+        <v/>
+      </c>
+      <c r="J310" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Specialist Manager - EOX Transformation and Optimization</v>
+      </c>
+      <c r="C311" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D311" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E311" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F311" t="str">
+        <v>$67.2B</v>
+      </c>
+      <c r="G311" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H311" t="str">
+        <v>https://in.linkedin.com/jobs/view/specialist-manager-eox-transformation-and-optimization-hyderabad-at-deloitte-4467509475</v>
+      </c>
+      <c r="I311" t="str">
+        <v/>
+      </c>
+      <c r="J311" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>Accenture services Pvt Ltd</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Business Transformation Manager</v>
+      </c>
+      <c r="C312" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D312" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E312" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F312" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G312" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H312" t="str">
+        <v>https://in.linkedin.com/jobs/view/business-transformation-manager-at-accenture-services-pvt-ltd-4472530574</v>
+      </c>
+      <c r="I312" t="str">
+        <v/>
+      </c>
+      <c r="J312" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>Portage Point Partners</v>
+      </c>
+      <c r="B313" t="str">
+        <v>Vice President, Performance Improvement</v>
+      </c>
+      <c r="C313" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D313" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E313" t="str">
+        <v>Restructuring Advisory</v>
+      </c>
+      <c r="F313" t="str">
+        <v>$200M+</v>
+      </c>
+      <c r="G313" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H313" t="str">
+        <v>https://in.linkedin.com/jobs/view/vice-president-performance-improvement-at-portage-point-partners-4473354098</v>
+      </c>
+      <c r="I313" t="str">
+        <v/>
+      </c>
+      <c r="J313" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>WorldQuant</v>
+      </c>
+      <c r="B314" t="str">
+        <v>Executive Assistant and Office Manager</v>
+      </c>
+      <c r="C314" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D314" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E314" t="str">
+        <v>Quantitative Finance</v>
+      </c>
+      <c r="F314" t="str">
+        <v>$500M+</v>
+      </c>
+      <c r="G314" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H314" t="str">
+        <v>https://in.linkedin.com/jobs/view/executive-assistant-and-office-manager-at-worldquant-4447553110</v>
+      </c>
+      <c r="I314" t="str">
+        <v/>
+      </c>
+      <c r="J314" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>Finkraft</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Executive Assistant - Founder's Office</v>
+      </c>
+      <c r="C315" t="str">
+        <v>Founder's Office</v>
+      </c>
+      <c r="D315" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E315" t="str">
+        <v>Fintech (GST)</v>
+      </c>
+      <c r="F315" t="str">
+        <v>$100M+</v>
+      </c>
+      <c r="G315" t="str">
+        <v>1-5 years</v>
+      </c>
+      <c r="H315" t="str">
+        <v>https://in.linkedin.com/jobs/view/executive-assistant-founder-s-office-at-finkraft-4433603899</v>
+      </c>
+      <c r="I315" t="str">
+        <v/>
+      </c>
+      <c r="J315" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Medline</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Sr Manager - Transformation, Transitions &amp; PMO</v>
+      </c>
+      <c r="C316" t="str">
+        <v>Sr Manager</v>
+      </c>
+      <c r="D316" t="str">
+        <v>Pune Division, Maharashtra, India</v>
+      </c>
+      <c r="E316" t="str">
+        <v>Medical Supplies</v>
+      </c>
+      <c r="F316" t="str">
+        <v>$20B+</v>
+      </c>
+      <c r="G316" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H316" t="str">
+        <v>https://in.linkedin.com/jobs/view/sr-manager-transformation-transitions-pmo-at-medline-4459517854</v>
+      </c>
+      <c r="I316" t="str">
+        <v/>
+      </c>
+      <c r="J316" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>Medline</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Senior Manager - Transformation, Transitions &amp; PMO</v>
+      </c>
+      <c r="C317" t="str">
+        <v>Sr Manager</v>
+      </c>
+      <c r="D317" t="str">
+        <v>Pune Division, Maharashtra, India</v>
+      </c>
+      <c r="E317" t="str">
+        <v>Medical Supplies</v>
+      </c>
+      <c r="F317" t="str">
+        <v>$20B+</v>
+      </c>
+      <c r="G317" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H317" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-manager-transformation-transitions-pmo-at-medline-4472920851</v>
+      </c>
+      <c r="I317" t="str">
+        <v/>
+      </c>
+      <c r="J317" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B318" t="str">
+        <v>Senior Associate - SaT - CHS - SaT - TCF - M&amp;A Advisory</v>
+      </c>
+      <c r="C318" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D318" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E318" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F318" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G318" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H318" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-associate-sat-chs-sat-tcf-m-a-advisory-mumbai-at-ey-4454175162</v>
+      </c>
+      <c r="I318" t="str">
+        <v/>
+      </c>
+      <c r="J318" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Associate - SaT - CHS - SaT - TCF - M&amp;A Advisory - New Delhi</v>
+      </c>
+      <c r="C319" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D319" t="str">
+        <v>Delhi, India</v>
+      </c>
+      <c r="E319" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F319" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G319" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H319" t="str">
+        <v>https://in.linkedin.com/jobs/view/associate-sat-chs-sat-tcf-m-a-advisory-new-delhi-at-ey-4467330485</v>
+      </c>
+      <c r="I319" t="str">
+        <v/>
+      </c>
+      <c r="J319" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Indigo Group</v>
+      </c>
+      <c r="B320" t="str">
+        <v>M&amp;A / Investment Due Diligence &amp; Execution Associate</v>
+      </c>
+      <c r="C320" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D320" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E320" t="str">
+        <v>Aviation</v>
+      </c>
+      <c r="F320" t="str">
+        <v>$6B+</v>
+      </c>
+      <c r="G320" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H320" t="str">
+        <v>https://in.linkedin.com/jobs/view/m-a-investment-due-diligence-execution-associate-at-indigo-group-4474245708</v>
+      </c>
+      <c r="I320" t="str">
+        <v/>
+      </c>
+      <c r="J320" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>ACL Digital</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Director of Business Development - Life Sciences</v>
+      </c>
+      <c r="C321" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D321" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E321" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F321" t="str">
+        <v>$500M+</v>
+      </c>
+      <c r="G321" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H321" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-of-business-development-life-sciences-at-acl-digital-4470010350</v>
+      </c>
+      <c r="I321" t="str">
+        <v/>
+      </c>
+      <c r="J321" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>ACL Digital</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Director of Business Development - GCC Sales</v>
+      </c>
+      <c r="C322" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D322" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E322" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F322" t="str">
+        <v>$500M+</v>
+      </c>
+      <c r="G322" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H322" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-of-business-development-gcc-sales-at-acl-digital-4470011396</v>
+      </c>
+      <c r="I322" t="str">
+        <v/>
+      </c>
+      <c r="J322" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Larsen &amp; Toubro</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Mergers and Acquisitions Analyst</v>
+      </c>
+      <c r="C323" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="D323" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E323" t="str">
+        <v>Engineering &amp; Construction</v>
+      </c>
+      <c r="F323" t="str">
+        <v>$23B+</v>
+      </c>
+      <c r="G323" t="str">
+        <v>0-2 years</v>
+      </c>
+      <c r="H323" t="str">
+        <v>https://in.linkedin.com/jobs/view/mergers-and-acquisitions-analyst-at-larsen-toubro-4467362249</v>
+      </c>
+      <c r="I323" t="str">
+        <v/>
+      </c>
+      <c r="J323" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Bain &amp; Company</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Associate - Mergers &amp; Acquisitions CoE</v>
+      </c>
+      <c r="C324" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D324" t="str">
+        <v>Delhi, Delhi, India</v>
+      </c>
+      <c r="E324" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F324" t="str">
+        <v>$6.5B+</v>
+      </c>
+      <c r="G324" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H324" t="str">
+        <v>https://in.linkedin.com/jobs/view/associate-mergers-acquisitions-coe-at-bain-company-4463177614</v>
+      </c>
+      <c r="I324" t="str">
+        <v/>
+      </c>
+      <c r="J324" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>Alvarez &amp; Marsal</v>
+      </c>
+      <c r="B325" t="str">
+        <v>Senior Associate - Consumer &amp; Retail Consulting</v>
+      </c>
+      <c r="C325" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D325" t="str">
+        <v>Greater Delhi Area</v>
+      </c>
+      <c r="E325" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F325" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G325" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H325" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-associate-consumer-retail-consulting-at-alvarez-marsal-4465975772</v>
+      </c>
+      <c r="I325" t="str">
+        <v/>
+      </c>
+      <c r="J325" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>Bain &amp; Company</v>
+      </c>
+      <c r="B326" t="str">
+        <v>Associate- Vector (Generalist)</v>
+      </c>
+      <c r="C326" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D326" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E326" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F326" t="str">
+        <v>$6.5B+</v>
+      </c>
+      <c r="G326" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H326" t="str">
+        <v>https://in.linkedin.com/jobs/view/associate-vector-generalist-at-bain-company-4438179596</v>
+      </c>
+      <c r="I326" t="str">
+        <v/>
+      </c>
+      <c r="J326" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>Bain &amp; Company</v>
+      </c>
+      <c r="B327" t="str">
+        <v>Associate- Vector (Generalist)</v>
+      </c>
+      <c r="C327" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D327" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E327" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F327" t="str">
+        <v>$6.5B+</v>
+      </c>
+      <c r="G327" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H327" t="str">
+        <v>https://in.linkedin.com/jobs/view/associate-vector-generalist-at-bain-company-4437142458</v>
+      </c>
+      <c r="I327" t="str">
+        <v/>
+      </c>
+      <c r="J327" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>PwC Acceleration Center India</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Advisory- Strategy and Value Creation - Procurement - Senior Associate</v>
+      </c>
+      <c r="C328" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D328" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E328" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F328" t="str">
+        <v>$55.4B</v>
+      </c>
+      <c r="G328" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H328" t="str">
+        <v>https://in.linkedin.com/jobs/view/advisory-strategy-and-value-creation-procurement-senior-associate-at-pwc-acceleration-center-india-4447308116</v>
+      </c>
+      <c r="I328" t="str">
+        <v/>
+      </c>
+      <c r="J328" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>Alvarez &amp; Marsal</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Senior Associate, CRG - Global Capability Center</v>
+      </c>
+      <c r="C329" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D329" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E329" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F329" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G329" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H329" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-associate-crg-global-capability-center-at-alvarez-marsal-4440982921</v>
+      </c>
+      <c r="I329" t="str">
+        <v/>
+      </c>
+      <c r="J329" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>Bain &amp; Company</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Associate - Mergers &amp; Acquisitions CoE</v>
+      </c>
+      <c r="C330" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D330" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E330" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F330" t="str">
+        <v>$6.5B+</v>
+      </c>
+      <c r="G330" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H330" t="str">
+        <v>https://in.linkedin.com/jobs/view/associate-mergers-acquisitions-coe-at-bain-company-4458220525</v>
+      </c>
+      <c r="I330" t="str">
+        <v/>
+      </c>
+      <c r="J330" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>BNP Paribas</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Head, Transversal Change Management</v>
+      </c>
+      <c r="C331" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D331" t="str">
+        <v>Chennai, Tamil Nadu, India</v>
+      </c>
+      <c r="E331" t="str">
+        <v>Banking</v>
+      </c>
+      <c r="F331" t="str">
+        <v>$50B+</v>
+      </c>
+      <c r="G331" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H331" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-change-management-at-bnp-paribas-4125553481</v>
+      </c>
+      <c r="I331" t="str">
+        <v/>
+      </c>
+      <c r="J331" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Medline</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Director Strategy</v>
+      </c>
+      <c r="C332" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D332" t="str">
+        <v>India</v>
+      </c>
+      <c r="E332" t="str">
+        <v>Medical Supplies</v>
+      </c>
+      <c r="F332" t="str">
+        <v>$20B+</v>
+      </c>
+      <c r="G332" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H332" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-strategy-at-medline-4322240760</v>
+      </c>
+      <c r="I332" t="str">
+        <v/>
+      </c>
+      <c r="J332" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>JPMorganChase</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Security &amp; Resiliency Initiative - VP</v>
+      </c>
+      <c r="C333" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D333" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E333" t="str">
+        <v>Banking &amp; Financial Services</v>
+      </c>
+      <c r="F333" t="str">
+        <v>$177.6B</v>
+      </c>
+      <c r="G333" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H333" t="str">
+        <v>https://in.linkedin.com/jobs/view/security-resiliency-vp-at-jpmorgan-4403158583</v>
+      </c>
+      <c r="I333" t="str">
+        <v/>
+      </c>
+      <c r="J333" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Portage Point Partners</v>
+      </c>
+      <c r="B334" t="str">
+        <v>VP, Turnaround &amp; Restructuring</v>
+      </c>
+      <c r="C334" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D334" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E334" t="str">
+        <v>Restructuring Advisory</v>
+      </c>
+      <c r="F334" t="str">
+        <v>$200M+</v>
+      </c>
+      <c r="G334" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H334" t="str">
+        <v>https://in.linkedin.com/jobs/view/vp-turnaround-restructuring-at-portage-point-4419555873</v>
+      </c>
+      <c r="I334" t="str">
+        <v/>
+      </c>
+      <c r="J334" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Cognizant</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Director- IOA - LAR</v>
+      </c>
+      <c r="C335" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D335" t="str">
+        <v>Gurgaon, Haryana, India</v>
+      </c>
+      <c r="E335" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F335" t="str">
+        <v>$19.4B</v>
+      </c>
+      <c r="G335" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H335" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-ioa-lar-at-cognizant-4423988441</v>
+      </c>
+      <c r="I335" t="str">
+        <v/>
+      </c>
+      <c r="J335" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>Tata Communications</v>
+      </c>
+      <c r="B336" t="str">
+        <v>General Manager - Sales - India</v>
+      </c>
+      <c r="C336" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D336" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E336" t="str">
+        <v>Telecom &amp; IT Services</v>
+      </c>
+      <c r="F336" t="str">
+        <v>$2.5B+</v>
+      </c>
+      <c r="G336" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H336" t="str">
+        <v>https://in.linkedin.com/jobs/view/gm-sales-india-at-tata-communications-4427767018</v>
+      </c>
+      <c r="I336" t="str">
+        <v/>
+      </c>
+      <c r="J336" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C337" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D337" t="str">
+        <v>India</v>
+      </c>
+      <c r="E337" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F337" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G337" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H337" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-ey-4434539850</v>
+      </c>
+      <c r="I337" t="str">
+        <v/>
+      </c>
+      <c r="J337" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B338" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C338" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D338" t="str">
+        <v>India</v>
+      </c>
+      <c r="E338" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F338" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G338" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H338" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-ey-2-4434549348</v>
+      </c>
+      <c r="I338" t="str">
+        <v/>
+      </c>
+      <c r="J338" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>LogiNext</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Vice President - Finance and Legal</v>
+      </c>
+      <c r="C339" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D339" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E339" t="str">
+        <v>Logistics SaaS</v>
+      </c>
+      <c r="F339" t="str">
+        <v>$100M+</v>
+      </c>
+      <c r="G339" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H339" t="str">
+        <v>https://in.linkedin.com/jobs/view/vice-president-finance-and-legal-at-loginext-4436716074</v>
+      </c>
+      <c r="I339" t="str">
+        <v/>
+      </c>
+      <c r="J339" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>Cvent</v>
+      </c>
+      <c r="B340" t="str">
+        <v>Director Strategy</v>
+      </c>
+      <c r="C340" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D340" t="str">
+        <v>India</v>
+      </c>
+      <c r="E340" t="str">
+        <v>Event Technology</v>
+      </c>
+      <c r="F340" t="str">
+        <v>$600M+</v>
+      </c>
+      <c r="G340" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H340" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-strategy-at-cvent-4440654721</v>
+      </c>
+      <c r="I340" t="str">
+        <v/>
+      </c>
+      <c r="J340" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>Coinbase</v>
+      </c>
+      <c r="B341" t="str">
+        <v>Country Director, India</v>
+      </c>
+      <c r="C341" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D341" t="str">
+        <v>India</v>
+      </c>
+      <c r="E341" t="str">
+        <v>Crypto Exchange</v>
+      </c>
+      <c r="F341" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G341" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H341" t="str">
+        <v>https://in.linkedin.com/jobs/view/country-director-india-at-coinbase-4443749991</v>
+      </c>
+      <c r="I341" t="str">
+        <v/>
+      </c>
+      <c r="J341" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>BlackRock</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Managing Director, Global Head PMS Engineering</v>
+      </c>
+      <c r="C342" t="str">
+        <v>MD/ED</v>
+      </c>
+      <c r="D342" t="str">
+        <v>Gurgaon, Haryana, India</v>
+      </c>
+      <c r="E342" t="str">
+        <v>Asset Management</v>
+      </c>
+      <c r="F342" t="str">
+        <v>$20B+</v>
+      </c>
+      <c r="G342" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H342" t="str">
+        <v>https://in.linkedin.com/jobs/view/md-global-head-pms-engineering-at-blackrock-4444955400</v>
+      </c>
+      <c r="I342" t="str">
+        <v/>
+      </c>
+      <c r="J342" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>PwC</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C343" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D343" t="str">
+        <v>India</v>
+      </c>
+      <c r="E343" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F343" t="str">
+        <v>$55.4B</v>
+      </c>
+      <c r="G343" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H343" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-pwc-4445064212</v>
+      </c>
+      <c r="I343" t="str">
+        <v/>
+      </c>
+      <c r="J343" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C344" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D344" t="str">
+        <v>India</v>
+      </c>
+      <c r="E344" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F344" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G344" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H344" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-accenture-5-4448318847</v>
+      </c>
+      <c r="I344" t="str">
+        <v/>
+      </c>
+      <c r="J344" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C345" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D345" t="str">
+        <v>India</v>
+      </c>
+      <c r="E345" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F345" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G345" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H345" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-accenture-3-4448323797</v>
+      </c>
+      <c r="I345" t="str">
+        <v/>
+      </c>
+      <c r="J345" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="B346" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C346" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D346" t="str">
+        <v>India</v>
+      </c>
+      <c r="E346" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F346" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G346" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H346" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-accenture-4-4448326453</v>
+      </c>
+      <c r="I346" t="str">
+        <v/>
+      </c>
+      <c r="J346" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Strategy Manager</v>
+      </c>
+      <c r="C347" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D347" t="str">
+        <v>India</v>
+      </c>
+      <c r="E347" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F347" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G347" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H347" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-manager-at-accenture-4448339592</v>
+      </c>
+      <c r="I347" t="str">
+        <v/>
+      </c>
+      <c r="J347" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Strategy Manager</v>
+      </c>
+      <c r="C348" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D348" t="str">
+        <v>India</v>
+      </c>
+      <c r="E348" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F348" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G348" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H348" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-manager-at-accenture-2-4448341597</v>
+      </c>
+      <c r="I348" t="str">
+        <v/>
+      </c>
+      <c r="J348" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C349" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D349" t="str">
+        <v>India</v>
+      </c>
+      <c r="E349" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F349" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G349" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H349" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-accenture-2-4448354296</v>
+      </c>
+      <c r="I349" t="str">
+        <v/>
+      </c>
+      <c r="J349" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C350" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D350" t="str">
+        <v>India</v>
+      </c>
+      <c r="E350" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F350" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G350" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H350" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-accenture-4448377077</v>
+      </c>
+      <c r="I350" t="str">
+        <v/>
+      </c>
+      <c r="J350" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Rolls-Royce</v>
+      </c>
+      <c r="B351" t="str">
+        <v>VP Programme Delivery &amp; PMO, GBS</v>
+      </c>
+      <c r="C351" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D351" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E351" t="str">
+        <v>Aerospace &amp; Defense</v>
+      </c>
+      <c r="F351" t="str">
+        <v>$18B+</v>
+      </c>
+      <c r="G351" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H351" t="str">
+        <v>https://in.linkedin.com/jobs/view/vp-programme-delivery-pmo-gbs-at-rolls-royce-4453131506</v>
+      </c>
+      <c r="I351" t="str">
+        <v/>
+      </c>
+      <c r="J351" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Ema</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Strategy Lead</v>
+      </c>
+      <c r="C352" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D352" t="str">
+        <v>India</v>
+      </c>
+      <c r="E352" t="str">
+        <v>FMCG</v>
+      </c>
+      <c r="F352" t="str">
+        <v>$500M+</v>
+      </c>
+      <c r="G352" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H352" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-lead-at-ema-4454659103</v>
+      </c>
+      <c r="I352" t="str">
+        <v/>
+      </c>
+      <c r="J352" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>AWS</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C353" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D353" t="str">
+        <v>India</v>
+      </c>
+      <c r="E353" t="str">
+        <v>Cloud Computing (Amazon)</v>
+      </c>
+      <c r="F353" t="str">
+        <v>$100B+</v>
+      </c>
+      <c r="G353" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H353" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-aws-4455794371</v>
+      </c>
+      <c r="I353" t="str">
+        <v/>
+      </c>
+      <c r="J353" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>AWS</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Sr Strategy Consultant</v>
+      </c>
+      <c r="C354" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D354" t="str">
+        <v>India</v>
+      </c>
+      <c r="E354" t="str">
+        <v>Cloud Computing (Amazon)</v>
+      </c>
+      <c r="F354" t="str">
+        <v>$100B+</v>
+      </c>
+      <c r="G354" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H354" t="str">
+        <v>https://in.linkedin.com/jobs/view/sr-strategy-consultant-at-aws-2-4455922190</v>
+      </c>
+      <c r="I354" t="str">
+        <v/>
+      </c>
+      <c r="J354" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>AWS</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Sr Strategy Consultant</v>
+      </c>
+      <c r="C355" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D355" t="str">
+        <v>India</v>
+      </c>
+      <c r="E355" t="str">
+        <v>Cloud Computing (Amazon)</v>
+      </c>
+      <c r="F355" t="str">
+        <v>$100B+</v>
+      </c>
+      <c r="G355" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H355" t="str">
+        <v>https://in.linkedin.com/jobs/view/sr-strategy-consultant-at-aws-4455924090</v>
+      </c>
+      <c r="I355" t="str">
+        <v/>
+      </c>
+      <c r="J355" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Amgen</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Director, RBQM Platforms &amp; Technology</v>
+      </c>
+      <c r="C356" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D356" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E356" t="str">
+        <v>Biotechnology</v>
+      </c>
+      <c r="F356" t="str">
+        <v>$27B+</v>
+      </c>
+      <c r="G356" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H356" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-rbqm-at-amgen-4457343880</v>
+      </c>
+      <c r="I356" t="str">
+        <v/>
+      </c>
+      <c r="J356" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="B357" t="str">
+        <v>M&amp;A Consultant</v>
+      </c>
+      <c r="C357" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D357" t="str">
+        <v>India</v>
+      </c>
+      <c r="E357" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F357" t="str">
+        <v>$67.2B</v>
+      </c>
+      <c r="G357" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H357" t="str">
+        <v>https://in.linkedin.com/jobs/view/ma-consultant-at-deloitte-4460970091</v>
+      </c>
+      <c r="I357" t="str">
+        <v/>
+      </c>
+      <c r="J357" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Corporate Strategy Manager</v>
+      </c>
+      <c r="C358" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D358" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E358" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F358" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G358" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H358" t="str">
+        <v>https://in.linkedin.com/jobs/view/corporate-strategy-manager-at-accenture-in-india-4461282020</v>
+      </c>
+      <c r="I358" t="str">
+        <v/>
+      </c>
+      <c r="J358" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>PwC</v>
+      </c>
+      <c r="B359" t="str">
+        <v>Senior Associate</v>
+      </c>
+      <c r="C359" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D359" t="str">
+        <v>India</v>
+      </c>
+      <c r="E359" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F359" t="str">
+        <v>$55.4B</v>
+      </c>
+      <c r="G359" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H359" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-associate-at-pwc-4462803408</v>
+      </c>
+      <c r="I359" t="str">
+        <v/>
+      </c>
+      <c r="J359" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Adani Group</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Business Development Lead</v>
+      </c>
+      <c r="C360" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D360" t="str">
+        <v>Ahmedabad, Gujarat, India</v>
+      </c>
+      <c r="E360" t="str">
+        <v>Conglomerate (Energy/Infra)</v>
+      </c>
+      <c r="F360" t="str">
+        <v>$30B+</v>
+      </c>
+      <c r="G360" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H360" t="str">
+        <v>https://in.linkedin.com/jobs/view/business-development-lead-at-adani-group-4463007121</v>
+      </c>
+      <c r="I360" t="str">
+        <v/>
+      </c>
+      <c r="J360" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="B361" t="str">
+        <v>EH-FY27-Consulting-S&amp;T-Strategy-Senior Consultant</v>
+      </c>
+      <c r="C361" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D361" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E361" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F361" t="str">
+        <v>$67.2B</v>
+      </c>
+      <c r="G361" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H361" t="str">
+        <v>https://in.linkedin.com/jobs/view/eh-fy27-consulting-s-t-strategy-senior-consultant-bs-consumer-at-deloitte-4463268049</v>
+      </c>
+      <c r="I361" t="str">
+        <v/>
+      </c>
+      <c r="J361" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="B362" t="str">
+        <v>EH-FY27-Consulting-S&amp;T-Strategy-Senior Consultant</v>
+      </c>
+      <c r="C362" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D362" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E362" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F362" t="str">
+        <v>$67.2B</v>
+      </c>
+      <c r="G362" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H362" t="str">
+        <v>https://in.linkedin.com/jobs/view/eh-fy27-consulting-s-t-strategy-senior-consultant-bs-consumer-at-deloitte-4463268051</v>
+      </c>
+      <c r="I362" t="str">
+        <v/>
+      </c>
+      <c r="J362" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Everest Group</v>
+      </c>
+      <c r="B363" t="str">
+        <v>VP - Commercial &amp; Solutions Analytics</v>
+      </c>
+      <c r="C363" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D363" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E363" t="str">
+        <v>Research &amp; Consulting</v>
+      </c>
+      <c r="F363" t="str">
+        <v>$100M+</v>
+      </c>
+      <c r="G363" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H363" t="str">
+        <v>https://in.linkedin.com/jobs/view/vp-commercial-solutions-analytics-at-everest-group-4463419398</v>
+      </c>
+      <c r="I363" t="str">
+        <v/>
+      </c>
+      <c r="J363" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>TCS</v>
+      </c>
+      <c r="B364" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C364" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D364" t="str">
+        <v>India</v>
+      </c>
+      <c r="E364" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F364" t="str">
+        <v>$29.1B</v>
+      </c>
+      <c r="G364" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H364" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-tcs-4464568669</v>
+      </c>
+      <c r="I364" t="str">
+        <v/>
+      </c>
+      <c r="J364" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>Apollo Tyres Ltd</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Divisional Head - Demand Planning</v>
+      </c>
+      <c r="C365" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D365" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E365" t="str">
+        <v>Tyres &amp; Automotive</v>
+      </c>
+      <c r="F365" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G365" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H365" t="str">
+        <v>https://in.linkedin.com/jobs/view/divisional-head-demand-planning-at-apollo-tyres-4465523655</v>
+      </c>
+      <c r="I365" t="str">
+        <v/>
+      </c>
+      <c r="J365" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>MUFG Pension &amp; Market Services</v>
+      </c>
+      <c r="B366" t="str">
+        <v>Head of Transformation</v>
+      </c>
+      <c r="C366" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D366" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E366" t="str">
+        <v>Banking &amp; Financial Services</v>
+      </c>
+      <c r="F366" t="str">
+        <v>$48B+</v>
+      </c>
+      <c r="G366" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H366" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-of-transformation-at-mufg-pms-4466074369</v>
+      </c>
+      <c r="I366" t="str">
+        <v/>
+      </c>
+      <c r="J366" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Jabil</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Director Strategy</v>
+      </c>
+      <c r="C367" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D367" t="str">
+        <v>India</v>
+      </c>
+      <c r="E367" t="str">
+        <v>Electronics Manufacturing</v>
+      </c>
+      <c r="F367" t="str">
+        <v>$34B+</v>
+      </c>
+      <c r="G367" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H367" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-strategy-at-jabil-4466189140</v>
+      </c>
+      <c r="I367" t="str">
+        <v/>
+      </c>
+      <c r="J367" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>Adani Group</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Business Development Head (Roads)</v>
+      </c>
+      <c r="C368" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D368" t="str">
+        <v>Ahmedabad, Gujarat, India</v>
+      </c>
+      <c r="E368" t="str">
+        <v>Conglomerate (Energy/Infra)</v>
+      </c>
+      <c r="F368" t="str">
+        <v>$30B+</v>
+      </c>
+      <c r="G368" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H368" t="str">
+        <v>https://in.linkedin.com/jobs/view/business-development-head-roads-at-adani-group-4467388692</v>
+      </c>
+      <c r="I368" t="str">
+        <v/>
+      </c>
+      <c r="J368" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>HSBC</v>
+      </c>
+      <c r="B369" t="str">
+        <v>SVP and Regional Head West India MSF</v>
+      </c>
+      <c r="C369" t="str">
+        <v>SVP</v>
+      </c>
+      <c r="D369" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E369" t="str">
+        <v>Banking</v>
+      </c>
+      <c r="F369" t="str">
+        <v>$66B+</v>
+      </c>
+      <c r="G369" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H369" t="str">
+        <v>https://in.linkedin.com/jobs/view/svp-regional-head-west-india-msf-at-hsbc-4467992707</v>
+      </c>
+      <c r="I369" t="str">
+        <v/>
+      </c>
+      <c r="J369" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>State Street</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Global Head FPS Operations, Senior MD</v>
+      </c>
+      <c r="C370" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D370" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E370" t="str">
+        <v>Financial Services</v>
+      </c>
+      <c r="F370" t="str">
+        <v>$12B+</v>
+      </c>
+      <c r="G370" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H370" t="str">
+        <v>https://in.linkedin.com/jobs/view/global-head-fps-operations-senior-md-at-state-street-4468308549</v>
+      </c>
+      <c r="I370" t="str">
+        <v/>
+      </c>
+      <c r="J370" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>State Street</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Global Head FPS Operations, Senior MD</v>
+      </c>
+      <c r="C371" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D371" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E371" t="str">
+        <v>Financial Services</v>
+      </c>
+      <c r="F371" t="str">
+        <v>$12B+</v>
+      </c>
+      <c r="G371" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H371" t="str">
+        <v>https://in.linkedin.com/jobs/view/global-head-fps-operations-senior-md-at-state-street-4468320391</v>
+      </c>
+      <c r="I371" t="str">
+        <v/>
+      </c>
+      <c r="J371" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Uber</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Head of Transformation, Field Operations</v>
+      </c>
+      <c r="C372" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D372" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E372" t="str">
+        <v>Mobility &amp; Delivery</v>
+      </c>
+      <c r="F372" t="str">
+        <v>$37B+</v>
+      </c>
+      <c r="G372" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H372" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-transformation-field-ops-at-uber-4468625835</v>
+      </c>
+      <c r="I372" t="str">
+        <v/>
+      </c>
+      <c r="J372" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>Uber</v>
+      </c>
+      <c r="B373" t="str">
+        <v>Head of Transformation, Field Operations</v>
+      </c>
+      <c r="C373" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D373" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E373" t="str">
+        <v>Mobility &amp; Delivery</v>
+      </c>
+      <c r="F373" t="str">
+        <v>$37B+</v>
+      </c>
+      <c r="G373" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H373" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-transformation-field-ops-at-uber-blr-4468644417</v>
+      </c>
+      <c r="I373" t="str">
+        <v/>
+      </c>
+      <c r="J373" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>Caterpillar</v>
+      </c>
+      <c r="B374" t="str">
+        <v>Strategy Manager</v>
+      </c>
+      <c r="C374" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D374" t="str">
+        <v>India</v>
+      </c>
+      <c r="E374" t="str">
+        <v>Heavy Machinery</v>
+      </c>
+      <c r="F374" t="str">
+        <v>$67B+</v>
+      </c>
+      <c r="G374" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H374" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-manager-at-caterpillar-4469185218</v>
+      </c>
+      <c r="I374" t="str">
+        <v/>
+      </c>
+      <c r="J374" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C375" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D375" t="str">
+        <v>India</v>
+      </c>
+      <c r="E375" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F375" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G375" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H375" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-ey-3-4469343590</v>
+      </c>
+      <c r="I375" t="str">
+        <v/>
+      </c>
+      <c r="J375" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>TCS</v>
+      </c>
+      <c r="B376" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C376" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D376" t="str">
+        <v>India</v>
+      </c>
+      <c r="E376" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F376" t="str">
+        <v>$29.1B</v>
+      </c>
+      <c r="G376" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H376" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-tcs-4470098502</v>
+      </c>
+      <c r="I376" t="str">
+        <v/>
+      </c>
+      <c r="J376" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B377" t="str">
+        <v>I&amp;P- GN- I&amp;E-Retail- Relex-Consultant</v>
+      </c>
+      <c r="C377" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D377" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E377" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F377" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G377" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H377" t="str">
+        <v>https://in.linkedin.com/jobs/view/i-p-gn-i-e-retail-relex-consultant-at-accenture-in-india-4470607793</v>
+      </c>
+      <c r="I377" t="str">
+        <v/>
+      </c>
+      <c r="J377" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>GMR Group</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Head Strategy</v>
+      </c>
+      <c r="C378" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D378" t="str">
+        <v>India</v>
+      </c>
+      <c r="E378" t="str">
+        <v>Infrastructure &amp; Airports</v>
+      </c>
+      <c r="F378" t="str">
+        <v>$2B+</v>
+      </c>
+      <c r="G378" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H378" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-strategy-at-gmr-group-4470900766</v>
+      </c>
+      <c r="I378" t="str">
+        <v/>
+      </c>
+      <c r="J378" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>Adit</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Strategy Manager</v>
+      </c>
+      <c r="C379" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D379" t="str">
+        <v>India</v>
+      </c>
+      <c r="E379" t="str">
+        <v>Conglomerate</v>
+      </c>
+      <c r="F379" t="str">
+        <v>$60B+</v>
+      </c>
+      <c r="G379" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H379" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-manager-at-adit-4470937616</v>
+      </c>
+      <c r="I379" t="str">
+        <v/>
+      </c>
+      <c r="J379" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Meesho</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Senior Manager, CEO's Office</v>
+      </c>
+      <c r="C380" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D380" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E380" t="str">
+        <v>Social Commerce</v>
+      </c>
+      <c r="F380" t="str">
+        <v>$300M+</v>
+      </c>
+      <c r="G380" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H380" t="str">
+        <v>https://in.linkedin.com/jobs/view/sr-manager-ceos-office-at-meesho-4470990019</v>
+      </c>
+      <c r="I380" t="str">
+        <v/>
+      </c>
+      <c r="J380" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>JPMorgan</v>
+      </c>
+      <c r="B381" t="str">
+        <v>VP Strategy</v>
+      </c>
+      <c r="C381" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D381" t="str">
+        <v>India</v>
+      </c>
+      <c r="E381" t="str">
+        <v>Banking &amp; Financial Services</v>
+      </c>
+      <c r="F381" t="str">
+        <v>$177.6B</v>
+      </c>
+      <c r="G381" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H381" t="str">
+        <v>https://in.linkedin.com/jobs/view/vp-strategy-at-jpmorgan-4471117570</v>
+      </c>
+      <c r="I381" t="str">
+        <v/>
+      </c>
+      <c r="J381" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B382" t="str">
+        <v>M&amp;A Consultant</v>
+      </c>
+      <c r="C382" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D382" t="str">
+        <v>India</v>
+      </c>
+      <c r="E382" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F382" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G382" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H382" t="str">
+        <v>https://in.linkedin.com/jobs/view/ma-consultant-at-ey-4471418850</v>
+      </c>
+      <c r="I382" t="str">
+        <v/>
+      </c>
+      <c r="J382" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>Wipro</v>
+      </c>
+      <c r="B383" t="str">
+        <v>GM - Global Head, Travel &amp; Hospitality</v>
+      </c>
+      <c r="C383" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D383" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E383" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F383" t="str">
+        <v>$10.8B</v>
+      </c>
+      <c r="G383" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H383" t="str">
+        <v>https://in.linkedin.com/jobs/view/gm-global-head-travel-hospitality-at-wipro-4471890537</v>
+      </c>
+      <c r="I383" t="str">
+        <v/>
+      </c>
+      <c r="J383" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Retail Management Consultant</v>
+      </c>
+      <c r="C384" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D384" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E384" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F384" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G384" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H384" t="str">
+        <v>https://in.linkedin.com/jobs/view/retail-management-consultant-at-infosys-4471992963</v>
+      </c>
+      <c r="I384" t="str">
+        <v/>
+      </c>
+      <c r="J384" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Knowledge Services Consultant</v>
+      </c>
+      <c r="C385" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D385" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E385" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F385" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G385" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H385" t="str">
+        <v>https://in.linkedin.com/jobs/view/knowledge-services-consultant-at-infosys-4472306306</v>
+      </c>
+      <c r="I385" t="str">
+        <v/>
+      </c>
+      <c r="J385" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Insurance Management Consultant</v>
+      </c>
+      <c r="C386" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D386" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E386" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F386" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G386" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H386" t="str">
+        <v>https://in.linkedin.com/jobs/view/insurance-management-consultant-at-infosys-4472312110</v>
+      </c>
+      <c r="I386" t="str">
+        <v/>
+      </c>
+      <c r="J386" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Wipro</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Strategy Manager</v>
+      </c>
+      <c r="C387" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D387" t="str">
+        <v>India</v>
+      </c>
+      <c r="E387" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F387" t="str">
+        <v>$10.8B</v>
+      </c>
+      <c r="G387" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H387" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-manager-at-wipro-4472424023</v>
+      </c>
+      <c r="I387" t="str">
+        <v/>
+      </c>
+      <c r="J387" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Zycus</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Country Director - India</v>
+      </c>
+      <c r="C388" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D388" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E388" t="str">
+        <v>Procurement Software</v>
+      </c>
+      <c r="F388" t="str">
+        <v>$200M+</v>
+      </c>
+      <c r="G388" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H388" t="str">
+        <v>https://in.linkedin.com/jobs/view/country-director-india-at-zycus-4472732855</v>
+      </c>
+      <c r="I388" t="str">
+        <v/>
+      </c>
+      <c r="J388" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>Zycus</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Country Director - India</v>
+      </c>
+      <c r="C389" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D389" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E389" t="str">
+        <v>Procurement Software</v>
+      </c>
+      <c r="F389" t="str">
+        <v>$200M+</v>
+      </c>
+      <c r="G389" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H389" t="str">
+        <v>https://in.linkedin.com/jobs/view/country-director-india-at-zycus-4472735511</v>
+      </c>
+      <c r="I389" t="str">
+        <v/>
+      </c>
+      <c r="J389" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>FNP</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Chief Operating Officer</v>
+      </c>
+      <c r="C390" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D390" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E390" t="str">
+        <v>E-commerce (Gifts)</v>
+      </c>
+      <c r="F390" t="str">
+        <v>$200M+</v>
+      </c>
+      <c r="G390" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H390" t="str">
+        <v>https://in.linkedin.com/jobs/view/chief-operating-officer-at-fnp-4472901123</v>
+      </c>
+      <c r="I390" t="str">
+        <v/>
+      </c>
+      <c r="J390" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Thermo Fisher</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C391" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D391" t="str">
+        <v>India</v>
+      </c>
+      <c r="E391" t="str">
+        <v>Life Sciences &amp; Diagnostics</v>
+      </c>
+      <c r="F391" t="str">
+        <v>$42.9B</v>
+      </c>
+      <c r="G391" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H391" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-thermo-fisher-4473212938</v>
+      </c>
+      <c r="I391" t="str">
+        <v/>
+      </c>
+      <c r="J391" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>JioStar</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Strategy Lead</v>
+      </c>
+      <c r="C392" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D392" t="str">
+        <v>India</v>
+      </c>
+      <c r="E392" t="str">
+        <v>Media &amp; Telecom (Reliance-Disney)</v>
+      </c>
+      <c r="F392" t="str">
+        <v>$100B+</v>
+      </c>
+      <c r="G392" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H392" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-lead-at-jiostar-4473652612</v>
+      </c>
+      <c r="I392" t="str">
+        <v/>
+      </c>
+      <c r="J392" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Director - Business Consulting PI - TMT - Chennai</v>
+      </c>
+      <c r="C393" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D393" t="str">
+        <v>Chennai, Tamil Nadu, India</v>
+      </c>
+      <c r="E393" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F393" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G393" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H393" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-business-consulting-tmt-at-ey-4473673959</v>
+      </c>
+      <c r="I393" t="str">
+        <v/>
+      </c>
+      <c r="J393" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Management Consultant</v>
+      </c>
+      <c r="C394" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D394" t="str">
+        <v>India</v>
+      </c>
+      <c r="E394" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F394" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G394" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H394" t="str">
+        <v>https://in.linkedin.com/jobs/view/management-consultant-at-infosys-4473880936</v>
+      </c>
+      <c r="I394" t="str">
+        <v/>
+      </c>
+      <c r="J394" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>FNP</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Chief Operating Officer</v>
+      </c>
+      <c r="C395" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D395" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E395" t="str">
+        <v>E-commerce (Gifts)</v>
+      </c>
+      <c r="F395" t="str">
+        <v>$200M+</v>
+      </c>
+      <c r="G395" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H395" t="str">
+        <v>https://in.linkedin.com/jobs/view/chief-operating-officer-at-fnp-4474101720</v>
+      </c>
+      <c r="I395" t="str">
+        <v/>
+      </c>
+      <c r="J395" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>Haleon</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Head of Transition and Project Management</v>
+      </c>
+      <c r="C396" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D396" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E396" t="str">
+        <v>Consumer Healthcare</v>
+      </c>
+      <c r="F396" t="str">
+        <v>$13B+</v>
+      </c>
+      <c r="G396" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H396" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-transition-pm-at-haleon-4474236850</v>
+      </c>
+      <c r="I396" t="str">
+        <v/>
+      </c>
+      <c r="J396" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>Adani Enterprises</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Strategy Lead</v>
+      </c>
+      <c r="C397" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D397" t="str">
+        <v>India</v>
+      </c>
+      <c r="E397" t="str">
+        <v>Conglomerate</v>
+      </c>
+      <c r="F397" t="str">
+        <v>$10B+</v>
+      </c>
+      <c r="G397" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H397" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-lead-at-adani-enterprises-4474692636</v>
+      </c>
+      <c r="I397" t="str">
+        <v/>
+      </c>
+      <c r="J397" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Adani Power</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Strategy Lead</v>
+      </c>
+      <c r="C398" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D398" t="str">
+        <v>India</v>
+      </c>
+      <c r="E398" t="str">
+        <v>Power (Adani)</v>
+      </c>
+      <c r="F398" t="str">
+        <v>$4B+</v>
+      </c>
+      <c r="G398" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H398" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-lead-at-adani-power-4474693329</v>
+      </c>
+      <c r="I398" t="str">
+        <v/>
+      </c>
+      <c r="J398" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>Johnson &amp; Johnson</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Sr. Director, Sol Architect, SC Tech</v>
+      </c>
+      <c r="C399" t="str">
+        <v>Sr Director</v>
+      </c>
+      <c r="D399" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E399" t="str">
+        <v>Healthcare &amp; Pharma</v>
+      </c>
+      <c r="F399" t="str">
+        <v>$85B+</v>
+      </c>
+      <c r="G399" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H399" t="str">
+        <v>https://in.linkedin.com/jobs/view/sr-director-sol-architect-at-jnj-4474775615</v>
+      </c>
+      <c r="I399" t="str">
+        <v/>
+      </c>
+      <c r="J399" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>Larsen &amp; Toubro</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Head - Project Management</v>
+      </c>
+      <c r="C400" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D400" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E400" t="str">
+        <v>Engineering &amp; Construction</v>
+      </c>
+      <c r="F400" t="str">
+        <v>$23B+</v>
+      </c>
+      <c r="G400" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H400" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-project-management-at-lt-blr-4475171795</v>
+      </c>
+      <c r="I400" t="str">
+        <v/>
+      </c>
+      <c r="J400" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>Visa</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Senior Director - Govt Advisory and Strategic Partnerships</v>
+      </c>
+      <c r="C401" t="str">
+        <v>Sr Director</v>
+      </c>
+      <c r="D401" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E401" t="str">
+        <v>Payments Technology</v>
+      </c>
+      <c r="F401" t="str">
+        <v>$32.7B</v>
+      </c>
+      <c r="G401" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H401" t="str">
+        <v>https://in.linkedin.com/jobs/view/sr-director-govt-advisory-strategic-partnerships-at-visa-4475174348</v>
+      </c>
+      <c r="I401" t="str">
+        <v/>
+      </c>
+      <c r="J401" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B402" t="str">
+        <v>Data Strategy Consultant</v>
+      </c>
+      <c r="C402" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D402" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E402" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F402" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G402" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H402" t="str">
+        <v>https://in.linkedin.com/jobs/view/data-strategy-consultant-at-infosys-4475440355</v>
+      </c>
+      <c r="I402" t="str">
+        <v/>
+      </c>
+      <c r="J402" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B403" t="str">
+        <v>Data Strategy Consultant</v>
+      </c>
+      <c r="C403" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D403" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E403" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F403" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G403" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H403" t="str">
+        <v>https://in.linkedin.com/jobs/view/data-strategy-consultant-at-infosys-4475440358</v>
+      </c>
+      <c r="I403" t="str">
+        <v/>
+      </c>
+      <c r="J403" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>Caterpillar</v>
+      </c>
+      <c r="B404" t="str">
+        <v>Director Strategy</v>
+      </c>
+      <c r="C404" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D404" t="str">
+        <v>India</v>
+      </c>
+      <c r="E404" t="str">
+        <v>Heavy Machinery</v>
+      </c>
+      <c r="F404" t="str">
+        <v>$67B+</v>
+      </c>
+      <c r="G404" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H404" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-strategy-at-caterpillar-4475876257</v>
+      </c>
+      <c r="I404" t="str">
+        <v/>
+      </c>
+      <c r="J404" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>TCS</v>
+      </c>
+      <c r="B405" t="str">
+        <v>Strategy Consultant</v>
+      </c>
+      <c r="C405" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D405" t="str">
+        <v>India</v>
+      </c>
+      <c r="E405" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F405" t="str">
+        <v>$29.1B</v>
+      </c>
+      <c r="G405" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H405" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-at-tcs-4476163271</v>
+      </c>
+      <c r="I405" t="str">
+        <v/>
+      </c>
+      <c r="J405" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>Intellectual Capital HR Consulting</v>
+      </c>
+      <c r="B406" t="str">
+        <v>VP Operations Institutional broking</v>
+      </c>
+      <c r="C406" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D406" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E406" t="str">
+        <v>Semiconductors</v>
+      </c>
+      <c r="F406" t="str">
+        <v>$54B+</v>
+      </c>
+      <c r="G406" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H406" t="str">
+        <v>https://in.linkedin.com/jobs/view/vp-operations-institutional-broking-at-intellectual-capital-4476595317</v>
+      </c>
+      <c r="I406" t="str">
+        <v/>
+      </c>
+      <c r="J406" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>Wipro</v>
+      </c>
+      <c r="B407" t="str">
+        <v>Strategy Manager</v>
+      </c>
+      <c r="C407" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D407" t="str">
+        <v>India</v>
+      </c>
+      <c r="E407" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F407" t="str">
+        <v>$10.8B</v>
+      </c>
+      <c r="G407" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H407" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-manager-at-wipro-4476767983</v>
+      </c>
+      <c r="I407" t="str">
+        <v/>
+      </c>
+      <c r="J407" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>Johnson &amp; Johnson</v>
+      </c>
+      <c r="B408" t="str">
+        <v>Sr Director - Process Excellence</v>
+      </c>
+      <c r="C408" t="str">
+        <v>Sr Director</v>
+      </c>
+      <c r="D408" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E408" t="str">
+        <v>Healthcare &amp; Pharma</v>
+      </c>
+      <c r="F408" t="str">
+        <v>$85B+</v>
+      </c>
+      <c r="G408" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H408" t="str">
+        <v>https://in.linkedin.com/jobs/view/sr-director-process-excellence-at-jnj-4477152021</v>
+      </c>
+      <c r="I408" t="str">
+        <v/>
+      </c>
+      <c r="J408" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>Larsen &amp; Toubro</v>
+      </c>
+      <c r="B409" t="str">
+        <v>Head - Project Management</v>
+      </c>
+      <c r="C409" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D409" t="str">
+        <v>Chorasi, Gujarat, India</v>
+      </c>
+      <c r="E409" t="str">
+        <v>Engineering &amp; Construction</v>
+      </c>
+      <c r="F409" t="str">
+        <v>$23B+</v>
+      </c>
+      <c r="G409" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H409" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-project-management-at-lt-4477173384</v>
+      </c>
+      <c r="I409" t="str">
+        <v/>
+      </c>
+      <c r="J409" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>Sandoz India</v>
+      </c>
+      <c r="B410" t="str">
+        <v>Head of Pipeline &amp; Launch Forecasting</v>
+      </c>
+      <c r="C410" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D410" t="str">
+        <v>Telangana, India</v>
+      </c>
+      <c r="E410" t="str">
+        <v>Generic Pharmaceuticals</v>
+      </c>
+      <c r="F410" t="str">
+        <v>$10B+</v>
+      </c>
+      <c r="G410" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H410" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-pipeline-launch-forecasting-at-sandoz-india-4477402698</v>
+      </c>
+      <c r="I410" t="str">
+        <v/>
+      </c>
+      <c r="J410" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>Emeritus</v>
+      </c>
+      <c r="B411" t="str">
+        <v>Chief of Staff</v>
+      </c>
+      <c r="C411" t="str">
+        <v>Chief of Staff</v>
+      </c>
+      <c r="D411" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E411" t="str">
+        <v>EdTech</v>
+      </c>
+      <c r="F411" t="str">
+        <v>$500M+</v>
+      </c>
+      <c r="G411" t="str">
+        <v>3-7 years</v>
+      </c>
+      <c r="H411" t="str">
+        <v>https://in.linkedin.com/jobs/view/chief-of-staff-at-emeritus-4477416210</v>
+      </c>
+      <c r="I411" t="str">
+        <v/>
+      </c>
+      <c r="J411" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>AB InBev India</v>
+      </c>
+      <c r="B412" t="str">
+        <v>AD- Strategy &amp; PMO</v>
+      </c>
+      <c r="C412" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D412" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E412" t="str">
+        <v>Beverages (FMCG)</v>
+      </c>
+      <c r="F412" t="str">
+        <v>$57.8B</v>
+      </c>
+      <c r="G412" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H412" t="str">
+        <v>https://in.linkedin.com/jobs/view/ad-strategy-pmo-at-ab-inbev-india-4475439374</v>
+      </c>
+      <c r="I412" t="str">
+        <v/>
+      </c>
+      <c r="J412" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>Abbott</v>
+      </c>
+      <c r="B413" t="str">
+        <v>Head - Commercial &amp; Strategic Planning</v>
+      </c>
+      <c r="C413" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D413" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E413" t="str">
+        <v>Healthcare &amp; Diagnostics</v>
+      </c>
+      <c r="F413" t="str">
+        <v>$40B+</v>
+      </c>
+      <c r="G413" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H413" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-commercial-strategic-planning-at-abbott-4457522817</v>
+      </c>
+      <c r="I413" t="str">
+        <v/>
+      </c>
+      <c r="J413" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B414" t="str">
+        <v>S&amp;C GN - Tech Strategy &amp; Transformation - TO VRO - Senior Manager</v>
+      </c>
+      <c r="C414" t="str">
+        <v>Sr Manager</v>
+      </c>
+      <c r="D414" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E414" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F414" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G414" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H414" t="str">
+        <v>https://in.linkedin.com/jobs/view/s-c-gn-tech-strategy-transformation-to-vro-senior-manager-at-accenture-in-india-4448351376</v>
+      </c>
+      <c r="I414" t="str">
+        <v/>
+      </c>
+      <c r="J414" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B415" t="str">
+        <v>#ACN S&amp;C GN - Tech Strategy &amp; Transformation - GCC - Manager</v>
+      </c>
+      <c r="C415" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D415" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E415" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F415" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G415" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H415" t="str">
+        <v>https://in.linkedin.com/jobs/view/%23acn-s-c-gn-tech-strategy-transformation-gcc-manager-at-accenture-in-india-4448353195</v>
+      </c>
+      <c r="I415" t="str">
+        <v/>
+      </c>
+      <c r="J415" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B416" t="str">
+        <v>S&amp;C GN - TS&amp;T – GCC - Consultant</v>
+      </c>
+      <c r="C416" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D416" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E416" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F416" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G416" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H416" t="str">
+        <v>https://in.linkedin.com/jobs/view/s-c-gn-ts-t-%E2%80%93-gcc-consultant-at-accenture-in-india-4468173316</v>
+      </c>
+      <c r="I416" t="str">
+        <v/>
+      </c>
+      <c r="J416" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B417" t="str">
+        <v>S&amp;C GN - TS&amp;T – Industry Techno &amp; Strategy Architect - Telco - Senior Manager</v>
+      </c>
+      <c r="C417" t="str">
+        <v>Sr Manager</v>
+      </c>
+      <c r="D417" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E417" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F417" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G417" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H417" t="str">
+        <v>https://in.linkedin.com/jobs/view/s-c-gn-ts-t-%E2%80%93-industry-techno-strategy-architect-telco-senior-manager-at-accenture-in-india-4448327938</v>
+      </c>
+      <c r="I417" t="str">
+        <v/>
+      </c>
+      <c r="J417" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B418" t="str">
+        <v>S&amp;C GN - TS&amp;T –  Industry Techno &amp; Strategy Architect - Telco - Consultant</v>
+      </c>
+      <c r="C418" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D418" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E418" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F418" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G418" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H418" t="str">
+        <v>https://in.linkedin.com/jobs/view/s-c-gn-ts-t-%E2%80%93-industry-techno-strategy-architect-telco-consultant-at-accenture-in-india-4448357299</v>
+      </c>
+      <c r="I418" t="str">
+        <v/>
+      </c>
+      <c r="J418" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B419" t="str">
+        <v>S&amp;C GN - TS&amp;T –Enterprise AI Value Strategy - Consultant</v>
+      </c>
+      <c r="C419" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D419" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E419" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F419" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G419" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H419" t="str">
+        <v>https://in.linkedin.com/jobs/view/s-c-gn-ts-t-%E2%80%93enterprise-ai-value-strategy-consultant-at-accenture-in-india-4450767585</v>
+      </c>
+      <c r="I419" t="str">
+        <v/>
+      </c>
+      <c r="J419" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>Accenture in India</v>
+      </c>
+      <c r="B420" t="str">
+        <v>S&amp;C GN - TS&amp;T –Enterprise AI Value Strategy - Consultant</v>
+      </c>
+      <c r="C420" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D420" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E420" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F420" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G420" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H420" t="str">
+        <v>https://in.linkedin.com/jobs/view/s-c-gn-ts-t-%E2%80%93enterprise-ai-value-strategy-consultant-at-accenture-in-india-4450767583</v>
+      </c>
+      <c r="I420" t="str">
+        <v/>
+      </c>
+      <c r="J420" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>Accenture services Pvt Ltd</v>
+      </c>
+      <c r="B421" t="str">
+        <v>IMU-SONG Strategy Manager</v>
+      </c>
+      <c r="C421" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D421" t="str">
+        <v>Delhi, Delhi, India</v>
+      </c>
+      <c r="E421" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F421" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G421" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H421" t="str">
+        <v>https://in.linkedin.com/jobs/view/imu-song-strategy-manager-at-accenture-services-pvt-ltd-4426227428</v>
+      </c>
+      <c r="I421" t="str">
+        <v/>
+      </c>
+      <c r="J421" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>Accenture services Pvt Ltd</v>
+      </c>
+      <c r="B422" t="str">
+        <v>IMU-SONG Strategy Consultant</v>
+      </c>
+      <c r="C422" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D422" t="str">
+        <v>Delhi, Delhi, India</v>
+      </c>
+      <c r="E422" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F422" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G422" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H422" t="str">
+        <v>https://in.linkedin.com/jobs/view/imu-song-strategy-consultant-at-accenture-services-pvt-ltd-4426214979</v>
+      </c>
+      <c r="I422" t="str">
+        <v/>
+      </c>
+      <c r="J422" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>Accenture services Pvt Ltd</v>
+      </c>
+      <c r="B423" t="str">
+        <v>S&amp;C GN - TS&amp;T –Enterprise AI Value Strategy - Consultant</v>
+      </c>
+      <c r="C423" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D423" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E423" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F423" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G423" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H423" t="str">
+        <v>https://in.linkedin.com/jobs/view/s-c-gn-ts-t-%E2%80%93enterprise-ai-value-strategy-consultant-at-accenture-services-pvt-ltd-4474206575</v>
+      </c>
+      <c r="I423" t="str">
+        <v/>
+      </c>
+      <c r="J423" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>Accenture services Pvt Ltd</v>
+      </c>
+      <c r="B424" t="str">
+        <v>S&amp;C GN - TS&amp;T –Enterprise AI Value Strategy - Consultant</v>
+      </c>
+      <c r="C424" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D424" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E424" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F424" t="str">
+        <v>$64.1B</v>
+      </c>
+      <c r="G424" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H424" t="str">
+        <v>https://in.linkedin.com/jobs/view/s-c-gn-ts-t-%E2%80%93enterprise-ai-value-strategy-consultant-at-accenture-services-pvt-ltd-4465468667</v>
+      </c>
+      <c r="I424" t="str">
+        <v/>
+      </c>
+      <c r="J424" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>Adani Group</v>
+      </c>
+      <c r="B425" t="str">
+        <v>BD and M&amp;A (Roads)</v>
+      </c>
+      <c r="C425" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D425" t="str">
+        <v>Ahmedabad, Gujarat, India</v>
+      </c>
+      <c r="E425" t="str">
+        <v>Conglomerate (Energy/Infra)</v>
+      </c>
+      <c r="F425" t="str">
+        <v>$30B+</v>
+      </c>
+      <c r="G425" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H425" t="str">
+        <v>https://in.linkedin.com/jobs/view/bd-and-m-a-roads-at-adani-group-4463044452</v>
+      </c>
+      <c r="I425" t="str">
+        <v/>
+      </c>
+      <c r="J425" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>Aditya Birla Sun Life Insurance</v>
+      </c>
+      <c r="B426" t="str">
+        <v>Strategy_Group Business_Mumbai</v>
+      </c>
+      <c r="C426" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D426" t="str">
+        <v>Maharashtra, India</v>
+      </c>
+      <c r="E426" t="str">
+        <v>Life Insurance (AB Group)</v>
+      </c>
+      <c r="F426" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G426" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H426" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-group-business-mumbai-at-aditya-birla-sun-life-insurance-4473910302</v>
+      </c>
+      <c r="I426" t="str">
+        <v/>
+      </c>
+      <c r="J426" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>Aditya Birla Sun Life Insurance</v>
+      </c>
+      <c r="B427" t="str">
+        <v>Strategy Lead - Axis</v>
+      </c>
+      <c r="C427" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D427" t="str">
+        <v>Maharashtra, India</v>
+      </c>
+      <c r="E427" t="str">
+        <v>Life Insurance (AB Group)</v>
+      </c>
+      <c r="F427" t="str">
+        <v>$3B+</v>
+      </c>
+      <c r="G427" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H427" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-lead-axis-at-aditya-birla-sun-life-insurance-4463363488</v>
+      </c>
+      <c r="I427" t="str">
+        <v/>
+      </c>
+      <c r="J427" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>Axis Finance Limited</v>
+      </c>
+      <c r="B428" t="str">
+        <v>Business Analyst:Business Strategy &amp; Analyst_AFL</v>
+      </c>
+      <c r="C428" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="D428" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E428" t="str">
+        <v>NBFC (Axis)</v>
+      </c>
+      <c r="F428" t="str">
+        <v>$1B+</v>
+      </c>
+      <c r="G428" t="str">
+        <v>0-2 years</v>
+      </c>
+      <c r="H428" t="str">
+        <v>https://in.linkedin.com/jobs/view/business-analyst-business-strategy-analyst-afl-at-axis-finance-limited-4439687292</v>
+      </c>
+      <c r="I428" t="str">
+        <v/>
+      </c>
+      <c r="J428" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>Bain &amp; Company</v>
+      </c>
+      <c r="B429" t="str">
+        <v>Associate- Vector(Tech and AI Strategy)</v>
+      </c>
+      <c r="C429" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D429" t="str">
+        <v>Delhi, Delhi, India</v>
+      </c>
+      <c r="E429" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F429" t="str">
+        <v>$6.5B+</v>
+      </c>
+      <c r="G429" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H429" t="str">
+        <v>https://in.linkedin.com/jobs/view/associate-vector-tech-and-ai-strategy-at-bain-company-4474299040</v>
+      </c>
+      <c r="I429" t="str">
+        <v/>
+      </c>
+      <c r="J429" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>Bain &amp; Company</v>
+      </c>
+      <c r="B430" t="str">
+        <v>Junior Consultant</v>
+      </c>
+      <c r="C430" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D430" t="str">
+        <v>Delhi Cantonment, Delhi, India</v>
+      </c>
+      <c r="E430" t="str">
+        <v>Management Consulting</v>
+      </c>
+      <c r="F430" t="str">
+        <v>$6.5B+</v>
+      </c>
+      <c r="G430" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H430" t="str">
+        <v>https://in.linkedin.com/jobs/view/junior-consultant-at-bain-company-4463120347</v>
+      </c>
+      <c r="I430" t="str">
+        <v/>
+      </c>
+      <c r="J430" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>Beckman Coulter Diagnostics</v>
+      </c>
+      <c r="B431" t="str">
+        <v>Strategic Marketing Leader – Diagnostics Platform India</v>
+      </c>
+      <c r="C431" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D431" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E431" t="str">
+        <v>Diagnostics (Danaher)</v>
+      </c>
+      <c r="F431" t="str">
+        <v>$7B+</v>
+      </c>
+      <c r="G431" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H431" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategic-marketing-leader-%E2%80%93-diagnostics-platform-india-at-beckman-coulter-diagnostics-4399964765</v>
+      </c>
+      <c r="I431" t="str">
+        <v/>
+      </c>
+      <c r="J431" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>Bristlecone</v>
+      </c>
+      <c r="B432" t="str">
+        <v>Senior Consultant - Consulting</v>
+      </c>
+      <c r="C432" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D432" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E432" t="str">
+        <v>Supply Chain Consulting (Mahindra)</v>
+      </c>
+      <c r="F432" t="str">
+        <v>$500M+</v>
+      </c>
+      <c r="G432" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H432" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-consultant-consulting-at-bristlecone-4267239875</v>
+      </c>
+      <c r="I432" t="str">
+        <v/>
+      </c>
+      <c r="J432" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>Bristlecone</v>
+      </c>
+      <c r="B433" t="str">
+        <v>Senior Consultant - Consulting</v>
+      </c>
+      <c r="C433" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D433" t="str">
+        <v>Pune Division, Maharashtra, India</v>
+      </c>
+      <c r="E433" t="str">
+        <v>Supply Chain Consulting (Mahindra)</v>
+      </c>
+      <c r="F433" t="str">
+        <v>$500M+</v>
+      </c>
+      <c r="G433" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H433" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-consultant-consulting-at-bristlecone-4264133394</v>
+      </c>
+      <c r="I433" t="str">
+        <v/>
+      </c>
+      <c r="J433" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>Bristlecone</v>
+      </c>
+      <c r="B434" t="str">
+        <v>Senior Consultant - Emerging Platforms</v>
+      </c>
+      <c r="C434" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D434" t="str">
+        <v>Pune Division, Maharashtra, India</v>
+      </c>
+      <c r="E434" t="str">
+        <v>Supply Chain Consulting (Mahindra)</v>
+      </c>
+      <c r="F434" t="str">
+        <v>$500M+</v>
+      </c>
+      <c r="G434" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H434" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-consultant-emerging-platforms-at-bristlecone-4217614506</v>
+      </c>
+      <c r="I434" t="str">
+        <v/>
+      </c>
+      <c r="J434" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="B435" t="str">
+        <v>Insurance Consulting -Senior Consultant</v>
+      </c>
+      <c r="C435" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D435" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E435" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F435" t="str">
+        <v>$22.5B</v>
+      </c>
+      <c r="G435" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H435" t="str">
+        <v>https://in.linkedin.com/jobs/view/insurance-consulting-senior-consultant-at-capgemini-4470966909</v>
+      </c>
+      <c r="I435" t="str">
+        <v/>
+      </c>
+      <c r="J435" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="B436" t="str">
+        <v>Financial Services Digital Customer Experience Strategy Leader - India</v>
+      </c>
+      <c r="C436" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D436" t="str">
+        <v>Pune Division, Maharashtra, India</v>
+      </c>
+      <c r="E436" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F436" t="str">
+        <v>$22.5B</v>
+      </c>
+      <c r="G436" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H436" t="str">
+        <v>https://in.linkedin.com/jobs/view/financial-services-digital-customer-experience-strategy-leader-india-at-capgemini-4409292923</v>
+      </c>
+      <c r="I436" t="str">
+        <v/>
+      </c>
+      <c r="J436" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="B437" t="str">
+        <v>Marketing Transformation - Senior Engagement Manager</v>
+      </c>
+      <c r="C437" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D437" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E437" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F437" t="str">
+        <v>$22.5B</v>
+      </c>
+      <c r="G437" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H437" t="str">
+        <v>https://in.linkedin.com/jobs/view/marketing-transformation-senior-engagement-manager-at-capgemini-4475784769</v>
+      </c>
+      <c r="I437" t="str">
+        <v/>
+      </c>
+      <c r="J437" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="B438" t="str">
+        <v>FBS Strategy Integration &amp; Reporting Analyst</v>
+      </c>
+      <c r="C438" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="D438" t="str">
+        <v>Pune Division, Maharashtra, India</v>
+      </c>
+      <c r="E438" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F438" t="str">
+        <v>$22.5B</v>
+      </c>
+      <c r="G438" t="str">
+        <v>0-2 years</v>
+      </c>
+      <c r="H438" t="str">
+        <v>https://in.linkedin.com/jobs/view/fbs-strategy-integration-reporting-analyst-at-capgemini-4408187058</v>
+      </c>
+      <c r="I438" t="str">
+        <v/>
+      </c>
+      <c r="J438" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="B439" t="str">
+        <v>Financial Services Digital Customer Experience Strategy Leader - India</v>
+      </c>
+      <c r="C439" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D439" t="str">
+        <v>Chennai, Tamil Nadu, India</v>
+      </c>
+      <c r="E439" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F439" t="str">
+        <v>$22.5B</v>
+      </c>
+      <c r="G439" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H439" t="str">
+        <v>https://in.linkedin.com/jobs/view/financial-services-digital-customer-experience-strategy-leader-india-at-capgemini-4409612091</v>
+      </c>
+      <c r="I439" t="str">
+        <v/>
+      </c>
+      <c r="J439" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="B440" t="str">
+        <v>Financial Services Digital Customer Experience Strategy Leader - India</v>
+      </c>
+      <c r="C440" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D440" t="str">
+        <v>Greater Kolkata Area</v>
+      </c>
+      <c r="E440" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F440" t="str">
+        <v>$22.5B</v>
+      </c>
+      <c r="G440" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H440" t="str">
+        <v>https://in.linkedin.com/jobs/view/financial-services-digital-customer-experience-strategy-leader-india-at-capgemini-4409600441</v>
+      </c>
+      <c r="I440" t="str">
+        <v/>
+      </c>
+      <c r="J440" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="B441" t="str">
+        <v>Financial Services Digital Customer Experience Strategy Leader - India</v>
+      </c>
+      <c r="C441" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D441" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E441" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F441" t="str">
+        <v>$22.5B</v>
+      </c>
+      <c r="G441" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H441" t="str">
+        <v>https://in.linkedin.com/jobs/view/financial-services-digital-customer-experience-strategy-leader-india-at-capgemini-4409600442</v>
+      </c>
+      <c r="I441" t="str">
+        <v/>
+      </c>
+      <c r="J441" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="B442" t="str">
+        <v>FBS Strategy Integration &amp; Reporting Analyst</v>
+      </c>
+      <c r="C442" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="D442" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E442" t="str">
+        <v>IT Services &amp; Consulting</v>
+      </c>
+      <c r="F442" t="str">
+        <v>$22.5B</v>
+      </c>
+      <c r="G442" t="str">
+        <v>0-2 years</v>
+      </c>
+      <c r="H442" t="str">
+        <v>https://in.linkedin.com/jobs/view/fbs-strategy-integration-reporting-analyst-at-capgemini-4408177102</v>
+      </c>
+      <c r="I442" t="str">
+        <v/>
+      </c>
+      <c r="J442" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>Citi</v>
+      </c>
+      <c r="B443" t="str">
+        <v>Strategy consultant with Market research</v>
+      </c>
+      <c r="C443" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D443" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E443" t="str">
+        <v>Banking &amp; Financial Services</v>
+      </c>
+      <c r="F443" t="str">
+        <v>$78.5B</v>
+      </c>
+      <c r="G443" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H443" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-with-market-research-at-citi-4475491897</v>
+      </c>
+      <c r="I443" t="str">
+        <v/>
+      </c>
+      <c r="J443" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>Deepak Group Co</v>
+      </c>
+      <c r="B444" t="str">
+        <v>Strategy Executive- Advanced Intermediates</v>
+      </c>
+      <c r="C444" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D444" t="str">
+        <v>Vadodara, Gujarat, India</v>
+      </c>
+      <c r="E444" t="str">
+        <v>Chemicals &amp; Infrastructure</v>
+      </c>
+      <c r="F444" t="str">
+        <v>$500M+</v>
+      </c>
+      <c r="G444" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H444" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-executive-advanced-intermediates-at-deepak-group-co-4474136234</v>
+      </c>
+      <c r="I444" t="str">
+        <v/>
+      </c>
+      <c r="J444" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="B445" t="str">
+        <v>EH-FY27-Consulting-S&amp;T-Strategy-Senior Consultant-BS-LS</v>
+      </c>
+      <c r="C445" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D445" t="str">
+        <v>Pune Division, Maharashtra, India</v>
+      </c>
+      <c r="E445" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F445" t="str">
+        <v>$67.2B</v>
+      </c>
+      <c r="G445" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H445" t="str">
+        <v>https://in.linkedin.com/jobs/view/eh-fy27-consulting-s-t-strategy-senior-consultant-bs-ls-at-deloitte-4463267070</v>
+      </c>
+      <c r="I445" t="str">
+        <v/>
+      </c>
+      <c r="J445" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="B446" t="str">
+        <v>EH-FY27-Consulting-S&amp;T-Strategy-Senior Consultant-TS-TMT</v>
+      </c>
+      <c r="C446" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D446" t="str">
+        <v>Chennai, Tamil Nadu, India</v>
+      </c>
+      <c r="E446" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F446" t="str">
+        <v>$67.2B</v>
+      </c>
+      <c r="G446" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H446" t="str">
+        <v>https://in.linkedin.com/jobs/view/eh-fy27-consulting-s-t-strategy-senior-consultant-ts-tmt-at-deloitte-4463261093</v>
+      </c>
+      <c r="I446" t="str">
+        <v/>
+      </c>
+      <c r="J446" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="B447" t="str">
+        <v>EH-FY27-Consulting-S&amp;T-Strategy-Senior Consultant-TS-TMT</v>
+      </c>
+      <c r="C447" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D447" t="str">
+        <v>Pune Division, Maharashtra, India</v>
+      </c>
+      <c r="E447" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F447" t="str">
+        <v>$67.2B</v>
+      </c>
+      <c r="G447" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H447" t="str">
+        <v>https://in.linkedin.com/jobs/view/eh-fy27-consulting-s-t-strategy-senior-consultant-ts-tmt-at-deloitte-4463272049</v>
+      </c>
+      <c r="I447" t="str">
+        <v/>
+      </c>
+      <c r="J447" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="B448" t="str">
+        <v>EH-FY27-Consulting-S&amp;T-Strategy-Senior Consultant-TS-FSI-IMRE</v>
+      </c>
+      <c r="C448" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D448" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E448" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F448" t="str">
+        <v>$67.2B</v>
+      </c>
+      <c r="G448" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H448" t="str">
+        <v>https://in.linkedin.com/jobs/view/eh-fy27-consulting-s-t-strategy-senior-consultant-ts-fsi-imre-at-deloitte-4463262087</v>
+      </c>
+      <c r="I448" t="str">
+        <v/>
+      </c>
+      <c r="J448" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="B449" t="str">
+        <v>EH-FY27-Consulting-S&amp;T-Strategy-Senior Consultant-TS-FSI-IMRE</v>
+      </c>
+      <c r="C449" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D449" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E449" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F449" t="str">
+        <v>$67.2B</v>
+      </c>
+      <c r="G449" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H449" t="str">
+        <v>https://in.linkedin.com/jobs/view/eh-fy27-consulting-s-t-strategy-senior-consultant-ts-fsi-imre-at-deloitte-4463262085</v>
+      </c>
+      <c r="I449" t="str">
+        <v/>
+      </c>
+      <c r="J449" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>ERM</v>
+      </c>
+      <c r="B450" t="str">
+        <v>Corporate Strategy Director</v>
+      </c>
+      <c r="C450" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D450" t="str">
+        <v>Greater Kolkata Area</v>
+      </c>
+      <c r="E450" t="str">
+        <v>Environmental Consulting</v>
+      </c>
+      <c r="F450" t="str">
+        <v>$800M+</v>
+      </c>
+      <c r="G450" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H450" t="str">
+        <v>https://in.linkedin.com/jobs/view/corporate-strategy-director-at-erm-4474452130</v>
+      </c>
+      <c r="I450" t="str">
+        <v/>
+      </c>
+      <c r="J450" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>EY</v>
+      </c>
+      <c r="B451" t="str">
+        <v>BC Sector - I and E-BUSINESS ACCELERATION-SM</v>
+      </c>
+      <c r="C451" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D451" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E451" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F451" t="str">
+        <v>$51.2B</v>
+      </c>
+      <c r="G451" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H451" t="str">
+        <v>https://in.linkedin.com/jobs/view/bc-sector-i-and-e-business-acceleration-sm-at-ey-4388055803</v>
+      </c>
+      <c r="I451" t="str">
+        <v/>
+      </c>
+      <c r="J451" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>FoxyMoron</v>
+      </c>
+      <c r="B452" t="str">
+        <v>Planning and Strategy Executive</v>
+      </c>
+      <c r="C452" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D452" t="str">
+        <v>Worli, Maharashtra, India</v>
+      </c>
+      <c r="E452" t="str">
+        <v>Digital Marketing</v>
+      </c>
+      <c r="F452" t="str">
+        <v>$100M+</v>
+      </c>
+      <c r="G452" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H452" t="str">
+        <v>https://in.linkedin.com/jobs/view/planning-and-strategy-executive-at-foxymoron-4464193074</v>
+      </c>
+      <c r="I452" t="str">
+        <v/>
+      </c>
+      <c r="J452" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>Havells India Ltd</v>
+      </c>
+      <c r="B453" t="str">
+        <v>CEO Office</v>
+      </c>
+      <c r="C453" t="str">
+        <v>CXO</v>
+      </c>
+      <c r="D453" t="str">
+        <v>Noida, Uttar Pradesh, India</v>
+      </c>
+      <c r="E453" t="str">
+        <v>Consumer Electricals</v>
+      </c>
+      <c r="F453" t="str">
+        <v>$2B+</v>
+      </c>
+      <c r="G453" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H453" t="str">
+        <v>https://in.linkedin.com/jobs/view/ceo-office-at-havells-india-ltd-4473620184</v>
+      </c>
+      <c r="I453" t="str">
+        <v/>
+      </c>
+      <c r="J453" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>HCLTech</v>
+      </c>
+      <c r="B454" t="str">
+        <v>AI Consultant: Physical AI GTM &amp; Solutions</v>
+      </c>
+      <c r="C454" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D454" t="str">
+        <v>Noida, Uttar Pradesh, India</v>
+      </c>
+      <c r="E454" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F454" t="str">
+        <v>$13.3B</v>
+      </c>
+      <c r="G454" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H454" t="str">
+        <v>https://in.linkedin.com/jobs/view/ai-consultant-physical-ai-gtm-solutions-at-hcltech-4459141215</v>
+      </c>
+      <c r="I454" t="str">
+        <v/>
+      </c>
+      <c r="J454" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>HCLTech</v>
+      </c>
+      <c r="B455" t="str">
+        <v>Vice President- SAP AI</v>
+      </c>
+      <c r="C455" t="str">
+        <v>VP</v>
+      </c>
+      <c r="D455" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E455" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F455" t="str">
+        <v>$13.3B</v>
+      </c>
+      <c r="G455" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H455" t="str">
+        <v>https://in.linkedin.com/jobs/view/vice-president-sap-ai-at-hcltech-4473146204</v>
+      </c>
+      <c r="I455" t="str">
+        <v/>
+      </c>
+      <c r="J455" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>HCLTech</v>
+      </c>
+      <c r="B456" t="str">
+        <v>AI Consultant: GTM &amp; Solutioning</v>
+      </c>
+      <c r="C456" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D456" t="str">
+        <v>Noida, Uttar Pradesh, India</v>
+      </c>
+      <c r="E456" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F456" t="str">
+        <v>$13.3B</v>
+      </c>
+      <c r="G456" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H456" t="str">
+        <v>https://in.linkedin.com/jobs/view/ai-consultant-gtm-solutioning-at-hcltech-4467705003</v>
+      </c>
+      <c r="I456" t="str">
+        <v/>
+      </c>
+      <c r="J456" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>HP</v>
+      </c>
+      <c r="B457" t="str">
+        <v>Head of Marketing Strategy, Planning and Operations</v>
+      </c>
+      <c r="C457" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D457" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E457" t="str">
+        <v>Technology</v>
+      </c>
+      <c r="F457" t="str">
+        <v>$53B+</v>
+      </c>
+      <c r="G457" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H457" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-of-marketing-strategy-planning-and-operations-at-hp-4449073778</v>
+      </c>
+      <c r="I457" t="str">
+        <v/>
+      </c>
+      <c r="J457" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>IBM</v>
+      </c>
+      <c r="B458" t="str">
+        <v>Strategy Consultant-Enterprise Strategy</v>
+      </c>
+      <c r="C458" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D458" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E458" t="str">
+        <v>Technology</v>
+      </c>
+      <c r="F458" t="str">
+        <v>$60B+</v>
+      </c>
+      <c r="G458" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H458" t="str">
+        <v>https://in.linkedin.com/jobs/view/strategy-consultant-enterprise-strategy-at-ibm-4474042402</v>
+      </c>
+      <c r="I458" t="str">
+        <v/>
+      </c>
+      <c r="J458" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>ICF</v>
+      </c>
+      <c r="B459" t="str">
+        <v>Cleantech Sector Specialist - Solar</v>
+      </c>
+      <c r="C459" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D459" t="str">
+        <v>New Delhi, Delhi, India</v>
+      </c>
+      <c r="E459" t="str">
+        <v>Consulting &amp; Digital Services</v>
+      </c>
+      <c r="F459" t="str">
+        <v>$2B+</v>
+      </c>
+      <c r="G459" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H459" t="str">
+        <v>https://in.linkedin.com/jobs/view/cleantech-sector-specialist-solar-at-icf-4472099477</v>
+      </c>
+      <c r="I459" t="str">
+        <v/>
+      </c>
+      <c r="J459" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>ICICI Lombard</v>
+      </c>
+      <c r="B460" t="str">
+        <v>AVP Health Governance &amp; Strategy</v>
+      </c>
+      <c r="C460" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="D460" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E460" t="str">
+        <v>General Insurance</v>
+      </c>
+      <c r="F460" t="str">
+        <v>$2B+</v>
+      </c>
+      <c r="G460" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H460" t="str">
+        <v>https://in.linkedin.com/jobs/view/avp-health-governance-strategy-at-icici-lombard-4465606753</v>
+      </c>
+      <c r="I460" t="str">
+        <v/>
+      </c>
+      <c r="J460" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>ICICI Securities</v>
+      </c>
+      <c r="B461" t="str">
+        <v>Manager - Business Planning &amp; Performance Improvement</v>
+      </c>
+      <c r="C461" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D461" t="str">
+        <v>Navi Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E461" t="str">
+        <v>Securities &amp; Broking</v>
+      </c>
+      <c r="F461" t="str">
+        <v>$1B+</v>
+      </c>
+      <c r="G461" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H461" t="str">
+        <v>https://in.linkedin.com/jobs/view/manager-business-planning-performance-improvement-at-icici-securities-4477116286</v>
+      </c>
+      <c r="I461" t="str">
+        <v/>
+      </c>
+      <c r="J461" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>IndusInd Bank</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Product Strategy Manager</v>
+      </c>
+      <c r="C462" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D462" t="str">
+        <v>Gurugram, Haryana, India</v>
+      </c>
+      <c r="E462" t="str">
+        <v>Banking</v>
+      </c>
+      <c r="F462" t="str">
+        <v>$5B+</v>
+      </c>
+      <c r="G462" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H462" t="str">
+        <v>https://in.linkedin.com/jobs/view/product-strategy-manager-at-indusind-bank-4463978748</v>
+      </c>
+      <c r="I462" t="str">
+        <v/>
+      </c>
+      <c r="J462" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Senior Principal - Business Consulting</v>
+      </c>
+      <c r="C463" t="str">
+        <v>Principal</v>
+      </c>
+      <c r="D463" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E463" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F463" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G463" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H463" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-principal-business-consulting-at-infosys-4471994799</v>
+      </c>
+      <c r="I463" t="str">
+        <v/>
+      </c>
+      <c r="J463" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B464" t="str">
+        <v>AI Strategic Consultant</v>
+      </c>
+      <c r="C464" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D464" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E464" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F464" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G464" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H464" t="str">
+        <v>https://in.linkedin.com/jobs/view/ai-strategic-consultant-at-infosys-4472549798</v>
+      </c>
+      <c r="I464" t="str">
+        <v/>
+      </c>
+      <c r="J464" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B465" t="str">
+        <v>Senior Consultant/Consultant – Banking Domain Consulting</v>
+      </c>
+      <c r="C465" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D465" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E465" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F465" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G465" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H465" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-consultant-consultant-%E2%80%93-banking-domain-consulting-at-infosys-4472569113</v>
+      </c>
+      <c r="I465" t="str">
+        <v/>
+      </c>
+      <c r="J465" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Financial Services Management Consultant</v>
+      </c>
+      <c r="C466" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D466" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E466" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F466" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G466" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H466" t="str">
+        <v>https://in.linkedin.com/jobs/view/financial-services-management-consultant-at-infosys-4471997628</v>
+      </c>
+      <c r="I466" t="str">
+        <v/>
+      </c>
+      <c r="J466" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Financial Services Management Consultant</v>
+      </c>
+      <c r="C467" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D467" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E467" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F467" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G467" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H467" t="str">
+        <v>https://in.linkedin.com/jobs/view/financial-services-management-consultant-at-infosys-4472303374</v>
+      </c>
+      <c r="I467" t="str">
+        <v/>
+      </c>
+      <c r="J467" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Product Manager/Consultant - Retail/Logistics/E-Commerce Domain</v>
+      </c>
+      <c r="C468" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D468" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E468" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F468" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G468" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H468" t="str">
+        <v>https://in.linkedin.com/jobs/view/product-manager-consultant-retail-logistics-e-commerce-domain-at-infosys-4443192615</v>
+      </c>
+      <c r="I468" t="str">
+        <v/>
+      </c>
+      <c r="J468" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="B469" t="str">
+        <v>Senior Consultant</v>
+      </c>
+      <c r="C469" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D469" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E469" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F469" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G469" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H469" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-consultant-at-infosys-4474963193</v>
+      </c>
+      <c r="I469" t="str">
+        <v/>
+      </c>
+      <c r="J469" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>Infosys Consulting</v>
+      </c>
+      <c r="B470" t="str">
+        <v>Senior Consultant / Principal – Business Consulting  (E/CTRM)</v>
+      </c>
+      <c r="C470" t="str">
+        <v>Principal</v>
+      </c>
+      <c r="D470" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E470" t="str">
+        <v>IT Consulting (Infosys)</v>
+      </c>
+      <c r="F470" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G470" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H470" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-consultant-principal-%E2%80%93-business-consulting-e-ctrm-at-infosys-consulting-4472110343</v>
+      </c>
+      <c r="I470" t="str">
+        <v/>
+      </c>
+      <c r="J470" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>Infosys Consulting</v>
+      </c>
+      <c r="B471" t="str">
+        <v>Business Consultant- IT Strategy</v>
+      </c>
+      <c r="C471" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D471" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E471" t="str">
+        <v>IT Consulting (Infosys)</v>
+      </c>
+      <c r="F471" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G471" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H471" t="str">
+        <v>https://in.linkedin.com/jobs/view/business-consultant-it-strategy-at-infosys-consulting-4469015026</v>
+      </c>
+      <c r="I471" t="str">
+        <v/>
+      </c>
+      <c r="J471" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>Infosys Consulting</v>
+      </c>
+      <c r="B472" t="str">
+        <v>Senior Consultant</v>
+      </c>
+      <c r="C472" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D472" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E472" t="str">
+        <v>IT Consulting (Infosys)</v>
+      </c>
+      <c r="F472" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G472" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H472" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-consultant-at-infosys-consulting-4469005159</v>
+      </c>
+      <c r="I472" t="str">
+        <v/>
+      </c>
+      <c r="J472" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>Infosys Consulting</v>
+      </c>
+      <c r="B473" t="str">
+        <v>Principal Consultant</v>
+      </c>
+      <c r="C473" t="str">
+        <v>Principal</v>
+      </c>
+      <c r="D473" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E473" t="str">
+        <v>IT Consulting (Infosys)</v>
+      </c>
+      <c r="F473" t="str">
+        <v>$18.6B</v>
+      </c>
+      <c r="G473" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H473" t="str">
+        <v>https://in.linkedin.com/jobs/view/principal-consultant-at-infosys-consulting-4469012042</v>
+      </c>
+      <c r="I473" t="str">
+        <v/>
+      </c>
+      <c r="J473" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>Jabil</v>
+      </c>
+      <c r="B474" t="str">
+        <v>Manager Digital Transformation</v>
+      </c>
+      <c r="C474" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D474" t="str">
+        <v>India</v>
+      </c>
+      <c r="E474" t="str">
+        <v>Electronics Manufacturing</v>
+      </c>
+      <c r="F474" t="str">
+        <v>$34B+</v>
+      </c>
+      <c r="G474" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H474" t="str">
+        <v>https://in.linkedin.com/jobs/view/manager-digital-transformation-at-jabil-4474617764</v>
+      </c>
+      <c r="I474" t="str">
+        <v/>
+      </c>
+      <c r="J474" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>JioStar</v>
+      </c>
+      <c r="B475" t="str">
+        <v>Manager - Product &amp; Revenue Strategy (Narratives), Sports</v>
+      </c>
+      <c r="C475" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D475" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E475" t="str">
+        <v>Media &amp; Telecom (Reliance-Disney)</v>
+      </c>
+      <c r="F475" t="str">
+        <v>$100B+</v>
+      </c>
+      <c r="G475" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H475" t="str">
+        <v>https://in.linkedin.com/jobs/view/manager-product-revenue-strategy-narratives-sports-at-jiostar-4429245226</v>
+      </c>
+      <c r="I475" t="str">
+        <v/>
+      </c>
+      <c r="J475" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>JioStar</v>
+      </c>
+      <c r="B476" t="str">
+        <v>Director - Sales Strategy, Distribution</v>
+      </c>
+      <c r="C476" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D476" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E476" t="str">
+        <v>Media &amp; Telecom (Reliance-Disney)</v>
+      </c>
+      <c r="F476" t="str">
+        <v>$100B+</v>
+      </c>
+      <c r="G476" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H476" t="str">
+        <v>https://in.linkedin.com/jobs/view/director-sales-strategy-distribution-at-jiostar-4453433301</v>
+      </c>
+      <c r="I476" t="str">
+        <v/>
+      </c>
+      <c r="J476" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>JioStar</v>
+      </c>
+      <c r="B477" t="str">
+        <v>Associate Director – Product &amp; Revenue Strategy, JioAds</v>
+      </c>
+      <c r="C477" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D477" t="str">
+        <v>Mumbai Metropolitan Region</v>
+      </c>
+      <c r="E477" t="str">
+        <v>Media &amp; Telecom (Reliance-Disney)</v>
+      </c>
+      <c r="F477" t="str">
+        <v>$100B+</v>
+      </c>
+      <c r="G477" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H477" t="str">
+        <v>https://in.linkedin.com/jobs/view/associate-director-%E2%80%93-product-revenue-strategy-jioads-at-jiostar-4470134594</v>
+      </c>
+      <c r="I477" t="str">
+        <v/>
+      </c>
+      <c r="J477" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
+        <v>JioStar</v>
+      </c>
+      <c r="B478" t="str">
+        <v>Senior Director - Entertainment PRS, Telugu</v>
+      </c>
+      <c r="C478" t="str">
+        <v>Sr Director</v>
+      </c>
+      <c r="D478" t="str">
+        <v>Hyderabad, Telangana, India</v>
+      </c>
+      <c r="E478" t="str">
+        <v>Media &amp; Telecom (Reliance-Disney)</v>
+      </c>
+      <c r="F478" t="str">
+        <v>$100B+</v>
+      </c>
+      <c r="G478" t="str">
+        <v>7+ years</v>
+      </c>
+      <c r="H478" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-director-entertainment-prs-telugu-at-jiostar-4435958835</v>
+      </c>
+      <c r="I478" t="str">
+        <v/>
+      </c>
+      <c r="J478" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>JioStar</v>
+      </c>
+      <c r="B479" t="str">
+        <v>Associate Director - Entertainment PRS, Star Plus &amp; Star Bharat</v>
+      </c>
+      <c r="C479" t="str">
+        <v>Director</v>
+      </c>
+      <c r="D479" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E479" t="str">
+        <v>Media &amp; Telecom (Reliance-Disney)</v>
+      </c>
+      <c r="F479" t="str">
+        <v>$100B+</v>
+      </c>
+      <c r="G479" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H479" t="str">
+        <v>https://in.linkedin.com/jobs/view/associate-director-entertainment-prs-star-plus-star-bharat-at-jiostar-4450430060</v>
+      </c>
+      <c r="I479" t="str">
+        <v/>
+      </c>
+      <c r="J479" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>Lupin</v>
+      </c>
+      <c r="B480" t="str">
+        <v>Business Development Manager</v>
+      </c>
+      <c r="C480" t="str">
+        <v>Manager/Lead</v>
+      </c>
+      <c r="D480" t="str">
+        <v>Pune District, Maharashtra, India</v>
+      </c>
+      <c r="E480" t="str">
+        <v>Pharmaceuticals</v>
+      </c>
+      <c r="F480" t="str">
+        <v>$2B+</v>
+      </c>
+      <c r="G480" t="str">
+        <v>3-6 years</v>
+      </c>
+      <c r="H480" t="str">
+        <v>https://in.linkedin.com/jobs/view/business-development-manager-at-lupin-4463809366</v>
+      </c>
+      <c r="I480" t="str">
+        <v/>
+      </c>
+      <c r="J480" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>NTT DATA North America</v>
+      </c>
+      <c r="B481" t="str">
+        <v>Senior Associate - Strategy &amp; Transformation Consulting</v>
+      </c>
+      <c r="C481" t="str">
+        <v>Sr Associate/Consultant</v>
+      </c>
+      <c r="D481" t="str">
+        <v>Noida, Uttar Pradesh, India</v>
+      </c>
+      <c r="E481" t="str">
+        <v>IT Services</v>
+      </c>
+      <c r="F481" t="str">
+        <v>$30B+</v>
+      </c>
+      <c r="G481" t="str">
+        <v>3-5 years</v>
+      </c>
+      <c r="H481" t="str">
+        <v>https://in.linkedin.com/jobs/view/senior-associate-strategy-transformation-consulting-at-ntt-data-north-america-4468369921</v>
+      </c>
+      <c r="I481" t="str">
+        <v/>
+      </c>
+      <c r="J481" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>PwC Acceleration Center India</v>
+      </c>
+      <c r="B482" t="str">
+        <v>Business Strategy &amp; Ops-Associate-Bangalore</v>
+      </c>
+      <c r="C482" t="str">
+        <v>Associate/Consultant</v>
+      </c>
+      <c r="D482" t="str">
+        <v>Bengaluru East, Karnataka, India</v>
+      </c>
+      <c r="E482" t="str">
+        <v>Professional Services</v>
+      </c>
+      <c r="F482" t="str">
+        <v>$55.4B</v>
+      </c>
+      <c r="G482" t="str">
+        <v>1-3 years</v>
+      </c>
+      <c r="H482" t="str">
+        <v>https://in.linkedin.com/jobs/view/business-strategy-ops-associate-bangalore-at-pwc-acceleration-center-india-4454121444</v>
+      </c>
+      <c r="I482" t="str">
+        <v/>
+      </c>
+      <c r="J482" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>Reliance Brands Limited</v>
+      </c>
+      <c r="B483" t="str">
+        <v>Head of Retail Operations</v>
+      </c>
+      <c r="C483" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D483" t="str">
+        <v>Mumbai, Maharashtra, India</v>
+      </c>
+      <c r="E483" t="str">
+        <v>Conglomerate</v>
+      </c>
+      <c r="F483" t="str">
+        <v>$100B+</v>
+      </c>
+      <c r="G483" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H483" t="str">
+        <v>https://in.linkedin.com/jobs/view/head-of-retail-operations-at-reliance-brands-limited-4474712211</v>
+      </c>
+      <c r="I483" t="str">
+        <v/>
+      </c>
+      <c r="J483" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>Tata Communications</v>
+      </c>
+      <c r="B484" t="str">
+        <v>Deputy General Manager</v>
+      </c>
+      <c r="C484" t="str">
+        <v>Head/GM</v>
+      </c>
+      <c r="D484" t="str">
+        <v>Bengaluru, Karnataka, India</v>
+      </c>
+      <c r="E484" t="str">
+        <v>Telecom &amp; IT Services</v>
+      </c>
+      <c r="F484" t="str">
+        <v>$2.5B+</v>
+      </c>
+      <c r="G484" t="str">
+        <v>5-7 years</v>
+      </c>
+      <c r="H484" t="str">
+        <v>https://in.linkedin.com/jobs/view/deputy-general-manager-at-tata-communications-4477113274</v>
+      </c>
+      <c r="I484" t="str">
+        <v/>
+      </c>
+      <c r="J484" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J234"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J484"/>
   </ignoredErrors>
 </worksheet>
 </file>